--- a/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_9_47.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_9_47.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4292602.704160014</v>
+        <v>4328911.495352372</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13275569.19337385</v>
+        <v>13283830.96054518</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13275569.19337385</v>
+        <v>13283830.96054518</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>603.5370117101811</v>
+        <v>5367.893211395565</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>603.5370117101811</v>
+        <v>5367.893211395565</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20558356.68881374</v>
+        <v>20557558.97656784</v>
       </c>
     </row>
   </sheetData>
@@ -669,13 +669,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935256937</v>
       </c>
       <c r="H2" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I2" t="n">
-        <v>1.79868786782652</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -702,16 +702,16 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.953406460792052</v>
       </c>
       <c r="S2" t="n">
-        <v>85.50414770182039</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T2" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -739,19 +739,19 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0491815260438</v>
+        <v>22.92014274264043</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -778,19 +778,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>145.073529241423</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R3" t="n">
-        <v>133.6519859716245</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S3" t="n">
-        <v>62.48881128536601</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T3" t="n">
-        <v>336.2273124936568</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U3" t="n">
-        <v>374</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -845,22 +845,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N4" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O4" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P4" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q4" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -906,13 +906,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H5" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.953406460791434</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>87.30283556964716</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T5" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U5" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,19 +1015,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R6" t="n">
-        <v>139.0130832731133</v>
+        <v>280.7594591068258</v>
       </c>
       <c r="S6" t="n">
-        <v>62.48881128536601</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T6" t="n">
-        <v>4.473444462796863</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N7" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O7" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P7" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q7" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1143,10 +1143,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H8" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1179,13 +1179,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>87.30283556964716</v>
+        <v>87.36594612241093</v>
       </c>
       <c r="T8" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U8" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1210,16 +1210,16 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>153.6008523136666</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1252,19 +1252,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>374</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S9" t="n">
-        <v>374</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T9" t="n">
-        <v>140.2836785810657</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
@@ -1319,22 +1319,22 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N10" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O10" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P10" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q10" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H11" t="n">
         <v>72.84688483418068</v>
@@ -1416,13 +1416,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>142.7955893384911</v>
+        <v>142.3350019731772</v>
       </c>
       <c r="T11" t="n">
         <v>259.6218731858503</v>
       </c>
       <c r="U11" t="n">
-        <v>328.1106633827815</v>
+        <v>328.5712507480957</v>
       </c>
       <c r="V11" t="n">
         <v>308.8510241668239</v>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>237.1483725282997</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C12" t="n">
-        <v>361.0999124455193</v>
+        <v>213.6917283274924</v>
       </c>
       <c r="D12" t="n">
         <v>347.9376868977026</v>
@@ -1456,13 +1456,13 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H12" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1492,16 +1492,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>180.333570877285</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S12" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T12" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V12" t="n">
         <v>93.51066719152016</v>
@@ -1553,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M13" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N13" t="n">
         <v>155.2579933044718</v>
@@ -1565,16 +1565,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P13" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q13" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S13" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>135.063180218145</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D15" t="n">
         <v>26.93768689770263</v>
@@ -1696,7 +1696,7 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>3.99961134672543</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H15" t="n">
         <v>4.021973978873973</v>
@@ -1726,13 +1726,13 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>180.333570877285</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S15" t="n">
-        <v>131.8202263797057</v>
+        <v>305.4120422616788</v>
       </c>
       <c r="T15" t="n">
         <v>81.3753501231742</v>
@@ -1750,7 +1750,7 @@
         <v>419.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="16">
@@ -1790,13 +1790,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>9.483546242607703</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M16" t="n">
         <v>102.3923982877958</v>
       </c>
       <c r="N16" t="n">
-        <v>155.2579933044718</v>
+        <v>154.4197474548741</v>
       </c>
       <c r="O16" t="n">
         <v>231.765039488851</v>
@@ -1857,10 +1857,10 @@
         <v>81.3744577141519</v>
       </c>
       <c r="H17" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949504</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1918,19 +1918,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>237.1483725282995</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D18" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G18" t="n">
         <v>3.99961134672543</v>
@@ -1963,13 +1963,13 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R18" t="n">
-        <v>180.333570877285</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S18" t="n">
-        <v>131.8202263797057</v>
+        <v>226.7834941523314</v>
       </c>
       <c r="T18" t="n">
         <v>81.3753501231742</v>
@@ -1981,7 +1981,7 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W18" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X18" t="n">
         <v>98.86273944538755</v>
@@ -2030,7 +2030,7 @@
         <v>10.32179209220538</v>
       </c>
       <c r="M19" t="n">
-        <v>101.5541524381981</v>
+        <v>102.3923982877958</v>
       </c>
       <c r="N19" t="n">
         <v>155.2579933044718</v>
@@ -2048,7 +2048,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S19" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>142.7955893384911</v>
+        <v>142.3350019731772</v>
       </c>
       <c r="T20" t="n">
         <v>259.6218731858503</v>
@@ -2161,19 +2161,19 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G21" t="n">
-        <v>3.999611346725456</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H21" t="n">
-        <v>98.98524175149976</v>
+        <v>98.9852417514997</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
         <v>79.16168051490372</v>
       </c>
       <c r="V21" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W21" t="n">
         <v>111.3731429098285</v>
@@ -2328,10 +2328,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H23" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S23" t="n">
         <v>142.3350019731772</v>
@@ -2392,13 +2392,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E24" t="n">
         <v>21.67209722191262</v>
@@ -2407,10 +2407,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G24" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H24" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2440,19 +2440,19 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>180.333570877285</v>
+        <v>353.9253867592582</v>
       </c>
       <c r="S24" t="n">
-        <v>131.8202263797056</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T24" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U24" t="n">
-        <v>79.16168051490372</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V24" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W24" t="n">
         <v>111.3731429098285</v>
@@ -2461,7 +2461,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>251.9832086481073</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="25">
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M25" t="n">
         <v>102.3923982877958</v>
@@ -2513,16 +2513,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P25" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q25" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S25" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H26" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>142.3350019731772</v>
+        <v>138.9147893384911</v>
       </c>
       <c r="T26" t="n">
         <v>259.6218731858503</v>
@@ -2629,16 +2629,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C27" t="n">
-        <v>361.0999124455193</v>
+        <v>135.0631802181451</v>
       </c>
       <c r="D27" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E27" t="n">
-        <v>245.984450801303</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F27" t="n">
         <v>18.63624233787687</v>
@@ -2650,7 +2650,7 @@
         <v>4.021973978873961</v>
       </c>
       <c r="I27" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2686,7 +2686,7 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U27" t="n">
-        <v>79.16168051490372</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V27" t="n">
         <v>93.51066719152016</v>
@@ -2698,7 +2698,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y27" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="28">
@@ -2750,13 +2750,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P28" t="n">
-        <v>290.5838154131063</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q28" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>377.7099312598396</v>
+        <v>376.8716854102423</v>
       </c>
       <c r="S28" t="n">
         <v>30.56285675203577</v>
@@ -2805,7 +2805,7 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H29" t="n">
-        <v>72.84688483418068</v>
+        <v>69.42667219968841</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2838,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>142.7955893384911</v>
+        <v>142.3350019731772</v>
       </c>
       <c r="T29" t="n">
         <v>259.6218731858503</v>
@@ -2866,16 +2866,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C30" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
         <v>18.63624233787687</v>
@@ -2911,19 +2911,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>275.2968386499108</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S30" t="n">
-        <v>452.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T30" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U30" t="n">
-        <v>400.1616805149037</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V30" t="n">
         <v>93.51066719152016</v>
@@ -2932,7 +2932,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>98.86273944538755</v>
+        <v>272.4545553273608</v>
       </c>
       <c r="Y30" t="n">
         <v>78.39139276613435</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>9.483546242607703</v>
+        <v>9.483546242608153</v>
       </c>
       <c r="M31" t="n">
         <v>102.3923982877958</v>
@@ -3045,7 +3045,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>142.3350019731772</v>
+        <v>138.9147893387378</v>
       </c>
       <c r="T32" t="n">
         <v>259.6218731858503</v>
@@ -3103,28 +3103,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>63.55655664632661</v>
+        <v>158.5198244189524</v>
       </c>
       <c r="C33" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D33" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F33" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
         <v>3.99961134672543</v>
       </c>
       <c r="H33" t="n">
-        <v>4.021973978873973</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I33" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3148,10 +3148,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R33" t="n">
-        <v>483.2744725660227</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S33" t="n">
         <v>131.8202263797057</v>
@@ -3160,10 +3160,10 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U33" t="n">
-        <v>400.1616805149037</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V33" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W33" t="n">
         <v>111.3731429098285</v>
@@ -3276,10 +3276,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H35" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>142.3350019731772</v>
+        <v>138.9147893388647</v>
       </c>
       <c r="T35" t="n">
         <v>259.6218731858503</v>
@@ -3343,25 +3343,25 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E36" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F36" t="n">
-        <v>192.2280582198502</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>3.999611346725456</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H36" t="n">
-        <v>4.021973978873961</v>
+        <v>228.3343275582643</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3385,19 +3385,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R36" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S36" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T36" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U36" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V36" t="n">
         <v>93.51066719152016</v>
@@ -3406,7 +3406,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y36" t="n">
         <v>78.39139276613435</v>
@@ -3449,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M37" t="n">
         <v>102.3923982877958</v>
@@ -3461,16 +3461,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P37" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q37" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S37" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090246813</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3513,10 +3513,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G38" t="n">
-        <v>81.37445771415189</v>
+        <v>77.95424507989598</v>
       </c>
       <c r="H38" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3577,25 +3577,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
-        <v>213.6917283274924</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G39" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H39" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3628,13 +3628,13 @@
         <v>180.333570877285</v>
       </c>
       <c r="S39" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T39" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U39" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V39" t="n">
         <v>93.51066719152016</v>
@@ -3643,10 +3643,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>98.86273944538755</v>
+        <v>272.4545553273606</v>
       </c>
       <c r="Y39" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="40">
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M40" t="n">
         <v>102.3923982877958</v>
@@ -3698,16 +3698,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P40" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q40" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S40" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090247554</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3750,13 +3750,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>81.37445771415189</v>
+        <v>77.95424507989598</v>
       </c>
       <c r="H41" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3823,16 +3823,16 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E42" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>177.5914272286987</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H42" t="n">
-        <v>325.021973978874</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3865,19 +3865,19 @@
         <v>180.333570877285</v>
       </c>
       <c r="S42" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T42" t="n">
-        <v>81.3753501231742</v>
+        <v>254.9671660051475</v>
       </c>
       <c r="U42" t="n">
-        <v>79.16168051490372</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V42" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X42" t="n">
         <v>98.86273944538755</v>
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M43" t="n">
         <v>102.3923982877958</v>
@@ -3935,16 +3935,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P43" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q43" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S43" t="n">
-        <v>29.72461090243842</v>
+        <v>29.724610902512</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>81.3744577141519</v>
+        <v>77.95424507989576</v>
       </c>
       <c r="H44" t="n">
         <v>72.84688483418068</v>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>142.7955893384911</v>
+        <v>142.3350019731772</v>
       </c>
       <c r="T44" t="n">
         <v>259.6218731858503</v>
@@ -4054,22 +4054,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>361.0999124455193</v>
+        <v>135.0631802181452</v>
       </c>
       <c r="D45" t="n">
-        <v>200.5295027796757</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H45" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4096,22 +4096,22 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R45" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S45" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T45" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U45" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V45" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W45" t="n">
         <v>111.3731429098285</v>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M46" t="n">
         <v>102.3923982877958</v>
@@ -4172,16 +4172,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P46" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q46" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S46" t="n">
-        <v>29.72461090243831</v>
+        <v>29.72461090252472</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108.731003807232</v>
+        <v>106.868499946019</v>
       </c>
       <c r="C2" t="n">
-        <v>58.7566823496624</v>
+        <v>56.89417848844941</v>
       </c>
       <c r="D2" t="n">
-        <v>48.31309069324847</v>
+        <v>46.45058683203548</v>
       </c>
       <c r="E2" t="n">
-        <v>43.90572745398721</v>
+        <v>42.04322359277423</v>
       </c>
       <c r="F2" t="n">
-        <v>38.96670855700554</v>
+        <v>37.10420469579255</v>
       </c>
       <c r="G2" t="n">
-        <v>35.58557518755106</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H2" t="n">
-        <v>31.736856432148</v>
+        <v>29.92</v>
       </c>
       <c r="I2" t="n">
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>29.92</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K2" t="n">
-        <v>81.5583303517588</v>
+        <v>400.2796902997726</v>
       </c>
       <c r="L2" t="n">
-        <v>145.6202453266332</v>
+        <v>464.9696632645968</v>
       </c>
       <c r="M2" t="n">
-        <v>515.8802453266331</v>
+        <v>835.2296632645968</v>
       </c>
       <c r="N2" t="n">
-        <v>886.1402453266331</v>
+        <v>1205.489663264597</v>
       </c>
       <c r="O2" t="n">
-        <v>886.1402453266331</v>
+        <v>1205.489663264597</v>
       </c>
       <c r="P2" t="n">
-        <v>1256.400245326633</v>
+        <v>1264.153869653468</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
       </c>
       <c r="R2" t="n">
-        <v>1496</v>
+        <v>1494.026862160816</v>
       </c>
       <c r="S2" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T2" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U2" t="n">
-        <v>971.1785586019998</v>
+        <v>969.3160547407869</v>
       </c>
       <c r="V2" t="n">
-        <v>739.0058069183393</v>
+        <v>737.1433030571263</v>
       </c>
       <c r="W2" t="n">
-        <v>498.2245180486953</v>
+        <v>496.3620141874823</v>
       </c>
       <c r="X2" t="n">
-        <v>304.0004438460006</v>
+        <v>302.1379399847876</v>
       </c>
       <c r="Y2" t="n">
-        <v>191.5585926512467</v>
+        <v>189.6960887900337</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>366.5169812739328</v>
+        <v>1079.463349058052</v>
       </c>
       <c r="C3" t="n">
-        <v>366.5169812739328</v>
+        <v>1079.463349058052</v>
       </c>
       <c r="D3" t="n">
-        <v>366.5169812739328</v>
+        <v>728.0111400704739</v>
       </c>
       <c r="E3" t="n">
-        <v>366.5169812739328</v>
+        <v>381.8777085331884</v>
       </c>
       <c r="F3" t="n">
-        <v>366.5169812739328</v>
+        <v>381.8777085331884</v>
       </c>
       <c r="G3" t="n">
-        <v>366.5169812739328</v>
+        <v>53.07165933600044</v>
       </c>
       <c r="H3" t="n">
-        <v>33.13396963146437</v>
+        <v>29.92</v>
       </c>
       <c r="I3" t="n">
-        <v>33.13396963146437</v>
+        <v>29.92</v>
       </c>
       <c r="J3" t="n">
-        <v>177.6113405614803</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K3" t="n">
-        <v>401.8775591086939</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L3" t="n">
-        <v>720.3885386284223</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M3" t="n">
-        <v>861.5031803712816</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N3" t="n">
-        <v>1051.274153846774</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O3" t="n">
-        <v>1341.994549492757</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P3" t="n">
-        <v>1496</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1349.46108157432</v>
+        <v>1349.538506374912</v>
       </c>
       <c r="R3" t="n">
-        <v>1214.459075542376</v>
+        <v>1214.671396474091</v>
       </c>
       <c r="S3" t="n">
-        <v>1151.339064143017</v>
+        <v>1151.591741468861</v>
       </c>
       <c r="T3" t="n">
-        <v>811.715516169626</v>
+        <v>1147.081868083532</v>
       </c>
       <c r="U3" t="n">
-        <v>433.9377383918481</v>
+        <v>1146.884106175968</v>
       </c>
       <c r="V3" t="n">
-        <v>419.2804988044541</v>
+        <v>1132.226866588574</v>
       </c>
       <c r="W3" t="n">
-        <v>386.5803544510919</v>
+        <v>1099.526722235211</v>
       </c>
       <c r="X3" t="n">
-        <v>366.5169812739328</v>
+        <v>1079.463349058052</v>
       </c>
       <c r="Y3" t="n">
-        <v>366.5169812739328</v>
+        <v>1079.463349058052</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1016.483548464727</v>
+        <v>505.7973598420842</v>
       </c>
       <c r="C4" t="n">
-        <v>1016.483548464727</v>
+        <v>505.7973598420842</v>
       </c>
       <c r="D4" t="n">
-        <v>1016.483548464727</v>
+        <v>505.7973598420842</v>
       </c>
       <c r="E4" t="n">
-        <v>1016.483548464727</v>
+        <v>573.9477435615022</v>
       </c>
       <c r="F4" t="n">
-        <v>1016.483548464727</v>
+        <v>698.3087161534377</v>
       </c>
       <c r="G4" t="n">
-        <v>1016.483548464727</v>
+        <v>851.8991623681918</v>
       </c>
       <c r="H4" t="n">
-        <v>1016.483548464727</v>
+        <v>1023.050610806278</v>
       </c>
       <c r="I4" t="n">
-        <v>1016.483548464727</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="J4" t="n">
-        <v>1386.743548464727</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K4" t="n">
-        <v>1386.743548464727</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L4" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M4" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N4" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O4" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P4" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q4" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R4" t="n">
         <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>29.92</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="T4" t="n">
-        <v>218.7737217817557</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="U4" t="n">
-        <v>465.3348468790587</v>
+        <v>505.7973598420842</v>
       </c>
       <c r="V4" t="n">
-        <v>664.1562397650047</v>
+        <v>505.7973598420842</v>
       </c>
       <c r="W4" t="n">
-        <v>836.0471580246821</v>
+        <v>505.7973598420842</v>
       </c>
       <c r="X4" t="n">
-        <v>987.0779490488756</v>
+        <v>505.7973598420842</v>
       </c>
       <c r="Y4" t="n">
-        <v>1016.483548464727</v>
+        <v>505.7973598420842</v>
       </c>
     </row>
     <row r="5">
@@ -4534,49 +4534,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106.914147375084</v>
+        <v>108.8416377852028</v>
       </c>
       <c r="C5" t="n">
-        <v>56.9398259175144</v>
+        <v>58.86731632763319</v>
       </c>
       <c r="D5" t="n">
-        <v>46.49623426110047</v>
+        <v>48.42372467121926</v>
       </c>
       <c r="E5" t="n">
-        <v>42.08887102183921</v>
+        <v>44.016361431958</v>
       </c>
       <c r="F5" t="n">
-        <v>37.14985212485754</v>
+        <v>39.07734253497633</v>
       </c>
       <c r="G5" t="n">
-        <v>33.76871875540306</v>
+        <v>35.70026987310013</v>
       </c>
       <c r="H5" t="n">
-        <v>29.92</v>
+        <v>31.89313783918327</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K5" t="n">
-        <v>400.18</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>464.2419149748744</v>
+        <v>835.1299729648241</v>
       </c>
       <c r="M5" t="n">
-        <v>834.5019149748744</v>
+        <v>1205.389972964824</v>
       </c>
       <c r="N5" t="n">
-        <v>1204.761914974874</v>
+        <v>1437.335793611129</v>
       </c>
       <c r="O5" t="n">
-        <v>1204.761914974874</v>
+        <v>1437.335793611129</v>
       </c>
       <c r="P5" t="n">
-        <v>1262.853806841132</v>
+        <v>1496</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4585,25 +4585,25 @@
         <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1407.815317606417</v>
+        <v>1409.724707412506</v>
       </c>
       <c r="T5" t="n">
-        <v>1221.067250178448</v>
+        <v>1222.994415731961</v>
       </c>
       <c r="U5" t="n">
-        <v>969.3617021698518</v>
+        <v>971.2891925799706</v>
       </c>
       <c r="V5" t="n">
-        <v>737.1889504861913</v>
+        <v>739.1164408963101</v>
       </c>
       <c r="W5" t="n">
-        <v>496.4076616165473</v>
+        <v>498.3351520266661</v>
       </c>
       <c r="X5" t="n">
-        <v>302.1835874138526</v>
+        <v>304.1110778239714</v>
       </c>
       <c r="Y5" t="n">
-        <v>189.7417362190987</v>
+        <v>191.6692266292175</v>
       </c>
     </row>
     <row r="6">
@@ -4613,76 +4613,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1070.572551977265</v>
+        <v>930.7350457196555</v>
       </c>
       <c r="C6" t="n">
-        <v>1070.572551977265</v>
+        <v>930.7350457196555</v>
       </c>
       <c r="D6" t="n">
-        <v>719.1203429896864</v>
+        <v>930.7350457196555</v>
       </c>
       <c r="E6" t="n">
-        <v>372.9869114524009</v>
+        <v>584.60161418237</v>
       </c>
       <c r="F6" t="n">
-        <v>29.92</v>
+        <v>241.534702729969</v>
       </c>
       <c r="G6" t="n">
-        <v>29.92</v>
+        <v>241.534702729969</v>
       </c>
       <c r="H6" t="n">
-        <v>29.92</v>
+        <v>241.534702729969</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
       </c>
       <c r="J6" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K6" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L6" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M6" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N6" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O6" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P6" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1346.247111942856</v>
+        <v>1349.538506374912</v>
       </c>
       <c r="R6" t="n">
-        <v>1205.829856111428</v>
+        <v>1065.943093135694</v>
       </c>
       <c r="S6" t="n">
-        <v>1142.709844712069</v>
+        <v>1002.863438130465</v>
       </c>
       <c r="T6" t="n">
-        <v>1138.191213941567</v>
+        <v>998.3535647451353</v>
       </c>
       <c r="U6" t="n">
-        <v>1137.99330909518</v>
+        <v>998.1558028375709</v>
       </c>
       <c r="V6" t="n">
-        <v>1123.336069507786</v>
+        <v>983.4985632501769</v>
       </c>
       <c r="W6" t="n">
-        <v>1090.635925154424</v>
+        <v>950.7984188968147</v>
       </c>
       <c r="X6" t="n">
-        <v>1070.572551977265</v>
+        <v>930.7350457196555</v>
       </c>
       <c r="Y6" t="n">
-        <v>1070.572551977265</v>
+        <v>930.7350457196555</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>876.4708337745928</v>
+        <v>851.8991623681918</v>
       </c>
       <c r="C7" t="n">
-        <v>876.4708337745928</v>
+        <v>851.8991623681918</v>
       </c>
       <c r="D7" t="n">
-        <v>876.4708337745928</v>
+        <v>851.8991623681918</v>
       </c>
       <c r="E7" t="n">
-        <v>876.4708337745928</v>
+        <v>851.8991623681918</v>
       </c>
       <c r="F7" t="n">
-        <v>876.4708337745928</v>
+        <v>851.8991623681918</v>
       </c>
       <c r="G7" t="n">
-        <v>876.4708337745928</v>
+        <v>851.8991623681918</v>
       </c>
       <c r="H7" t="n">
-        <v>876.4708337745928</v>
+        <v>1023.050610806278</v>
       </c>
       <c r="I7" t="n">
-        <v>1103.079808448381</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="J7" t="n">
-        <v>1255.222976822941</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K7" t="n">
-        <v>1386.743548464727</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L7" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M7" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N7" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O7" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P7" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q7" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R7" t="n">
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>70.34367574991084</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="T7" t="n">
-        <v>259.1973975316665</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="U7" t="n">
-        <v>505.7585226289696</v>
+        <v>505.7973598420842</v>
       </c>
       <c r="V7" t="n">
-        <v>704.5799155149155</v>
+        <v>704.6187527280301</v>
       </c>
       <c r="W7" t="n">
-        <v>876.4708337745928</v>
+        <v>851.8991623681918</v>
       </c>
       <c r="X7" t="n">
-        <v>876.4708337745928</v>
+        <v>851.8991623681918</v>
       </c>
       <c r="Y7" t="n">
-        <v>876.4708337745928</v>
+        <v>851.8991623681918</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>106.914147375084</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C8" t="n">
-        <v>56.9398259175144</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D8" t="n">
-        <v>46.49623426110047</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E8" t="n">
-        <v>42.08887102183921</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F8" t="n">
-        <v>37.14985212485754</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G8" t="n">
-        <v>33.76871875540306</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H8" t="n">
         <v>29.92</v>
@@ -4798,19 +4798,19 @@
         <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>770.4399999999999</v>
+        <v>452.3245884924623</v>
       </c>
       <c r="L8" t="n">
-        <v>834.5019149748742</v>
+        <v>517.0145614572864</v>
       </c>
       <c r="M8" t="n">
-        <v>1067.648108133742</v>
+        <v>887.2745614572864</v>
       </c>
       <c r="N8" t="n">
-        <v>1067.648108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="O8" t="n">
-        <v>1067.648108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P8" t="n">
         <v>1125.74</v>
@@ -4822,25 +4822,25 @@
         <v>1496</v>
       </c>
       <c r="S8" t="n">
-        <v>1407.815317606417</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T8" t="n">
-        <v>1221.067250178448</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U8" t="n">
-        <v>969.3617021698518</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V8" t="n">
-        <v>737.1889504861913</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W8" t="n">
-        <v>496.4076616165473</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X8" t="n">
-        <v>302.1835874138526</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y8" t="n">
-        <v>189.7417362190987</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="9">
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>381.3722089875785</v>
+        <v>1225.724928051676</v>
       </c>
       <c r="C9" t="n">
-        <v>381.3722089875785</v>
+        <v>1070.572551977265</v>
       </c>
       <c r="D9" t="n">
-        <v>29.92</v>
+        <v>719.1203429896864</v>
       </c>
       <c r="E9" t="n">
-        <v>29.92</v>
+        <v>372.9869114524009</v>
       </c>
       <c r="F9" t="n">
         <v>29.92</v>
@@ -4874,52 +4874,52 @@
         <v>29.92</v>
       </c>
       <c r="J9" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K9" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L9" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M9" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N9" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P9" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1346.247111942856</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="R9" t="n">
-        <v>968.469334165078</v>
+        <v>1360.932975467714</v>
       </c>
       <c r="S9" t="n">
-        <v>590.6915563873001</v>
+        <v>1297.853320462485</v>
       </c>
       <c r="T9" t="n">
-        <v>448.9908709518803</v>
+        <v>1293.343447077155</v>
       </c>
       <c r="U9" t="n">
-        <v>448.7929661054938</v>
+        <v>1293.145685169591</v>
       </c>
       <c r="V9" t="n">
-        <v>434.1357265180997</v>
+        <v>1278.488445582197</v>
       </c>
       <c r="W9" t="n">
-        <v>401.4355821647376</v>
+        <v>1245.788301228835</v>
       </c>
       <c r="X9" t="n">
-        <v>381.3722089875785</v>
+        <v>1225.724928051676</v>
       </c>
       <c r="Y9" t="n">
-        <v>381.3722089875785</v>
+        <v>1225.724928051676</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1210.2445873942</v>
+        <v>584.9895720284376</v>
       </c>
       <c r="C10" t="n">
-        <v>1268.914644253314</v>
+        <v>584.9895720284376</v>
       </c>
       <c r="D10" t="n">
-        <v>1268.914644253314</v>
+        <v>698.3087161534377</v>
       </c>
       <c r="E10" t="n">
-        <v>1386.743548464727</v>
+        <v>698.3087161534377</v>
       </c>
       <c r="F10" t="n">
-        <v>1386.743548464727</v>
+        <v>698.3087161534377</v>
       </c>
       <c r="G10" t="n">
-        <v>1386.743548464727</v>
+        <v>851.8991623681918</v>
       </c>
       <c r="H10" t="n">
-        <v>1386.743548464727</v>
+        <v>1023.050610806278</v>
       </c>
       <c r="I10" t="n">
-        <v>1386.743548464727</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="J10" t="n">
-        <v>1386.743548464727</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K10" t="n">
-        <v>1386.743548464727</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L10" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M10" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N10" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O10" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P10" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q10" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R10" t="n">
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>29.92</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="T10" t="n">
-        <v>218.7737217817557</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="U10" t="n">
-        <v>465.3348468790587</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="V10" t="n">
-        <v>664.1562397650047</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="W10" t="n">
-        <v>836.0471580246821</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="X10" t="n">
-        <v>987.0779490488756</v>
+        <v>410.2669283919256</v>
       </c>
       <c r="Y10" t="n">
-        <v>1098.487249727908</v>
+        <v>521.6762290709579</v>
       </c>
     </row>
     <row r="11">
@@ -5020,7 +5020,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F11" t="n">
-        <v>207.6991338872046</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G11" t="n">
         <v>125.5027119537179</v>
@@ -5032,16 +5032,16 @@
         <v>51.92</v>
       </c>
       <c r="J11" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K11" t="n">
-        <v>737.2059437357115</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L11" t="n">
-        <v>953.2578922784251</v>
+        <v>1844.448527309012</v>
       </c>
       <c r="M11" t="n">
-        <v>1595.767892278425</v>
+        <v>1844.448527309012</v>
       </c>
       <c r="N11" t="n">
         <v>2238.277892278425</v>
@@ -5059,10 +5059,10 @@
         <v>2596</v>
       </c>
       <c r="S11" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T11" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U11" t="n">
         <v>1858.092802114017</v>
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1141.180125483445</v>
+        <v>668.0405455662465</v>
       </c>
       <c r="C12" t="n">
-        <v>776.43273917484</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D12" t="n">
-        <v>424.9805301872616</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E12" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F12" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G12" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H12" t="n">
         <v>51.92</v>
@@ -5135,28 +5135,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R12" t="n">
-        <v>2062.032218270268</v>
+        <v>1737.789794027844</v>
       </c>
       <c r="S12" t="n">
-        <v>1928.880474452383</v>
+        <v>1604.638050209959</v>
       </c>
       <c r="T12" t="n">
-        <v>1846.683151095642</v>
+        <v>1522.440726853217</v>
       </c>
       <c r="U12" t="n">
-        <v>1766.721857646244</v>
+        <v>1442.479433403819</v>
       </c>
       <c r="V12" t="n">
-        <v>1672.26663826087</v>
+        <v>1348.024214018445</v>
       </c>
       <c r="W12" t="n">
-        <v>1559.768514109528</v>
+        <v>1235.526089867104</v>
       </c>
       <c r="X12" t="n">
-        <v>1459.907161134389</v>
+        <v>1135.664736891965</v>
       </c>
       <c r="Y12" t="n">
-        <v>1380.723936118092</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="13">
@@ -5199,22 +5199,22 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M13" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N13" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O13" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P13" t="n">
-        <v>819.9299076645212</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R13" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S13" t="n">
         <v>51.92</v>
@@ -5275,19 +5275,19 @@
         <v>307.5796384907274</v>
       </c>
       <c r="L14" t="n">
-        <v>950.0896384907273</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M14" t="n">
-        <v>1592.599638490728</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N14" t="n">
-        <v>2235.109638490728</v>
+        <v>1170.453074689115</v>
       </c>
       <c r="O14" t="n">
-        <v>2396.239739873683</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P14" t="n">
-        <v>2592.831746212303</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q14" t="n">
         <v>2596</v>
@@ -5324,19 +5324,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>264.3753454557945</v>
+        <v>492.6952769985969</v>
       </c>
       <c r="C15" t="n">
-        <v>127.9478906899915</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D15" t="n">
-        <v>100.7381059448373</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E15" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F15" t="n">
-        <v>60.0226114399994</v>
+        <v>384.2650356824237</v>
       </c>
       <c r="G15" t="n">
         <v>55.98259997866058</v>
@@ -5369,31 +5369,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q15" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R15" t="n">
-        <v>1982.60944240224</v>
+        <v>1737.789794027844</v>
       </c>
       <c r="S15" t="n">
-        <v>1849.457698584356</v>
+        <v>1429.292781642309</v>
       </c>
       <c r="T15" t="n">
-        <v>1767.260375227614</v>
+        <v>1347.095458285568</v>
       </c>
       <c r="U15" t="n">
-        <v>1687.299081778216</v>
+        <v>1267.13416483617</v>
       </c>
       <c r="V15" t="n">
-        <v>1592.843862392842</v>
+        <v>1172.678945450796</v>
       </c>
       <c r="W15" t="n">
-        <v>1480.3457382415</v>
+        <v>1060.180821299454</v>
       </c>
       <c r="X15" t="n">
-        <v>1056.241961023937</v>
+        <v>636.0770440818908</v>
       </c>
       <c r="Y15" t="n">
-        <v>652.8163117652153</v>
+        <v>556.8938190655934</v>
       </c>
     </row>
     <row r="16">
@@ -5433,10 +5433,10 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L16" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M16" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N16" t="n">
         <v>1349.248439584877</v>
@@ -5500,31 +5500,31 @@
         <v>125.9679517166617</v>
       </c>
       <c r="H17" t="n">
-        <v>52.3852397629438</v>
+        <v>51.92</v>
       </c>
       <c r="I17" t="n">
         <v>51.92</v>
       </c>
       <c r="J17" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K17" t="n">
-        <v>307.5796384907274</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L17" t="n">
-        <v>523.631587033441</v>
+        <v>1376.091327711023</v>
       </c>
       <c r="M17" t="n">
-        <v>1166.141587033441</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N17" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O17" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P17" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q17" t="n">
         <v>2596</v>
@@ -5561,16 +5561,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1141.180125483445</v>
+        <v>492.6952769985969</v>
       </c>
       <c r="C18" t="n">
-        <v>776.43273917484</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D18" t="n">
-        <v>749.2229544296858</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E18" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F18" t="n">
         <v>60.0226114399994</v>
@@ -5606,31 +5606,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q18" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R18" t="n">
-        <v>2062.032218270268</v>
+        <v>1658.367018159816</v>
       </c>
       <c r="S18" t="n">
-        <v>1928.880474452383</v>
+        <v>1429.292781642309</v>
       </c>
       <c r="T18" t="n">
-        <v>1846.683151095641</v>
+        <v>1347.095458285568</v>
       </c>
       <c r="U18" t="n">
-        <v>1766.721857646244</v>
+        <v>1267.13416483617</v>
       </c>
       <c r="V18" t="n">
-        <v>1672.26663826087</v>
+        <v>1172.678945450796</v>
       </c>
       <c r="W18" t="n">
-        <v>1559.768514109528</v>
+        <v>735.9383970570298</v>
       </c>
       <c r="X18" t="n">
-        <v>1459.907161134389</v>
+        <v>636.0770440818908</v>
       </c>
       <c r="Y18" t="n">
-        <v>1380.723936118091</v>
+        <v>556.8938190655934</v>
       </c>
     </row>
     <row r="19">
@@ -5673,22 +5673,22 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M19" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N19" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O19" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P19" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q19" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R19" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S19" t="n">
         <v>51.92</v>
@@ -5719,25 +5719,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C20" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D20" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E20" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F20" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G20" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H20" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I20" t="n">
         <v>51.92</v>
@@ -5746,22 +5746,22 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K20" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L20" t="n">
-        <v>950.0896384907273</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M20" t="n">
-        <v>1592.599638490728</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N20" t="n">
-        <v>2235.109638490728</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O20" t="n">
-        <v>2396.239739873683</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P20" t="n">
-        <v>2592.831746212303</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q20" t="n">
         <v>2596</v>
@@ -5770,25 +5770,25 @@
         <v>2596</v>
       </c>
       <c r="S20" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T20" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U20" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V20" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W20" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X20" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y20" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="21">
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>912.8601939406431</v>
+        <v>1237.102618183067</v>
       </c>
       <c r="C21" t="n">
-        <v>872.355231874462</v>
+        <v>1196.597656116886</v>
       </c>
       <c r="D21" t="n">
-        <v>845.1454471293079</v>
+        <v>845.1454471293077</v>
       </c>
       <c r="E21" t="n">
-        <v>499.0120155920224</v>
+        <v>499.0120155920222</v>
       </c>
       <c r="F21" t="n">
-        <v>155.9451041396214</v>
+        <v>480.1875283820456</v>
       </c>
       <c r="G21" t="n">
-        <v>151.9050926782826</v>
+        <v>151.9050926782825</v>
       </c>
       <c r="H21" t="n">
         <v>51.92</v>
@@ -5858,16 +5858,16 @@
         <v>1687.299081778216</v>
       </c>
       <c r="V21" t="n">
-        <v>1268.601438150418</v>
+        <v>1592.843862392842</v>
       </c>
       <c r="W21" t="n">
-        <v>1156.103313999076</v>
+        <v>1480.3457382415</v>
       </c>
       <c r="X21" t="n">
-        <v>1056.241961023937</v>
+        <v>1380.484385266361</v>
       </c>
       <c r="Y21" t="n">
-        <v>977.0587360076396</v>
+        <v>1301.301160250064</v>
       </c>
     </row>
     <row r="22">
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C23" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D23" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E23" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F23" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G23" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H23" t="n">
         <v>51.92</v>
@@ -5980,52 +5980,52 @@
         <v>51.92</v>
       </c>
       <c r="J23" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K23" t="n">
-        <v>733.5813277110226</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L23" t="n">
-        <v>949.6332762537361</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M23" t="n">
-        <v>1592.143276253736</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N23" t="n">
-        <v>2234.653276253736</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="O23" t="n">
-        <v>2395.783377636692</v>
+        <v>1367.045081027735</v>
       </c>
       <c r="P23" t="n">
-        <v>2592.375383975311</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q23" t="n">
         <v>2596</v>
       </c>
       <c r="R23" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S23" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T23" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U23" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V23" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W23" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X23" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y23" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="24">
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>816.9377012410212</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C24" t="n">
-        <v>452.1903149324157</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D24" t="n">
         <v>100.7381059448373</v>
@@ -6047,10 +6047,10 @@
         <v>78.84709864997603</v>
       </c>
       <c r="F24" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G24" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H24" t="n">
         <v>51.92</v>
@@ -6083,28 +6083,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R24" t="n">
-        <v>2062.032218270268</v>
+        <v>1886.686949702618</v>
       </c>
       <c r="S24" t="n">
-        <v>1928.880474452383</v>
+        <v>1429.292781642309</v>
       </c>
       <c r="T24" t="n">
-        <v>1846.683151095642</v>
+        <v>1347.095458285567</v>
       </c>
       <c r="U24" t="n">
-        <v>1766.721857646244</v>
+        <v>942.8917405937455</v>
       </c>
       <c r="V24" t="n">
-        <v>1672.26663826087</v>
+        <v>524.1940969659473</v>
       </c>
       <c r="W24" t="n">
-        <v>1559.768514109528</v>
+        <v>411.6959728146054</v>
       </c>
       <c r="X24" t="n">
-        <v>1459.907161134389</v>
+        <v>311.8346198394665</v>
       </c>
       <c r="Y24" t="n">
-        <v>1205.378667550442</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="25">
@@ -6156,13 +6156,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P25" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R25" t="n">
-        <v>81.94485949741255</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S25" t="n">
         <v>51.92</v>
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>597.1205880922939</v>
+        <v>596.5753483293503</v>
       </c>
       <c r="C26" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8030470738009</v>
       </c>
       <c r="D26" t="n">
-        <v>377.1067153823507</v>
+        <v>376.5614756194071</v>
       </c>
       <c r="E26" t="n">
-        <v>292.9013723451097</v>
+        <v>292.3561325821661</v>
       </c>
       <c r="F26" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6191338872046</v>
       </c>
       <c r="G26" t="n">
-        <v>125.9679517166614</v>
+        <v>125.4227119537179</v>
       </c>
       <c r="H26" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I26" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J26" t="n">
-        <v>133.4268380887174</v>
+        <v>133.3468380887174</v>
       </c>
       <c r="K26" t="n">
-        <v>737.2059437357115</v>
+        <v>307.4996384907275</v>
       </c>
       <c r="L26" t="n">
-        <v>953.2578922784251</v>
+        <v>523.551587033441</v>
       </c>
       <c r="M26" t="n">
-        <v>1595.767892278425</v>
+        <v>1006.31297330616</v>
       </c>
       <c r="N26" t="n">
-        <v>2238.277892278425</v>
+        <v>1647.83297330616</v>
       </c>
       <c r="O26" t="n">
-        <v>2399.40799366138</v>
+        <v>1808.963074689115</v>
       </c>
       <c r="P26" t="n">
-        <v>2596</v>
+        <v>2005.555081027735</v>
       </c>
       <c r="Q26" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R26" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="S26" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.682030971221</v>
       </c>
       <c r="T26" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.437714621877</v>
       </c>
       <c r="U26" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.012802114017</v>
       </c>
       <c r="V26" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.042070632377</v>
       </c>
       <c r="W26" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.462801964753</v>
       </c>
       <c r="X26" t="n">
-        <v>951.9859877270221</v>
+        <v>951.4407479640786</v>
       </c>
       <c r="Y26" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2009169713448</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1237.102618183067</v>
+        <v>264.2953454557946</v>
       </c>
       <c r="C27" t="n">
-        <v>872.3552318744619</v>
+        <v>127.8678906899915</v>
       </c>
       <c r="D27" t="n">
-        <v>520.9030228868835</v>
+        <v>100.6581059448373</v>
       </c>
       <c r="E27" t="n">
-        <v>272.4338806633451</v>
+        <v>78.76709864997605</v>
       </c>
       <c r="F27" t="n">
-        <v>253.6093934533685</v>
+        <v>59.94261143999941</v>
       </c>
       <c r="G27" t="n">
-        <v>249.5693819920296</v>
+        <v>55.90259997866057</v>
       </c>
       <c r="H27" t="n">
-        <v>245.506782013369</v>
+        <v>51.84</v>
       </c>
       <c r="I27" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J27" t="n">
-        <v>245.0840952696386</v>
+        <v>245.0040952696386</v>
       </c>
       <c r="K27" t="n">
-        <v>552.5636804206258</v>
+        <v>552.4836804206258</v>
       </c>
       <c r="L27" t="n">
-        <v>982.9653005063919</v>
+        <v>982.885300506392</v>
       </c>
       <c r="M27" t="n">
-        <v>1254.651042249251</v>
+        <v>1254.571042249251</v>
       </c>
       <c r="N27" t="n">
-        <v>1578.44894421531</v>
+        <v>1578.36894421531</v>
       </c>
       <c r="O27" t="n">
-        <v>1991.777795144312</v>
+        <v>1991.697795144312</v>
       </c>
       <c r="P27" t="n">
-        <v>2244.187340368535</v>
+        <v>2244.107340368535</v>
       </c>
       <c r="Q27" t="n">
-        <v>2164.764564500508</v>
+        <v>2164.684564500508</v>
       </c>
       <c r="R27" t="n">
-        <v>1982.60944240224</v>
+        <v>1982.52944240224</v>
       </c>
       <c r="S27" t="n">
-        <v>1849.457698584356</v>
+        <v>1849.377698584356</v>
       </c>
       <c r="T27" t="n">
-        <v>1767.260375227614</v>
+        <v>1767.180375227614</v>
       </c>
       <c r="U27" t="n">
-        <v>1687.299081778216</v>
+        <v>1362.976657535792</v>
       </c>
       <c r="V27" t="n">
-        <v>1592.843862392842</v>
+        <v>1268.521438150418</v>
       </c>
       <c r="W27" t="n">
-        <v>1480.3457382415</v>
+        <v>1156.023313999076</v>
       </c>
       <c r="X27" t="n">
-        <v>1380.484385266361</v>
+        <v>1056.161961023937</v>
       </c>
       <c r="Y27" t="n">
-        <v>1301.301160250064</v>
+        <v>652.7363117652154</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>686.6440969023969</v>
+        <v>686.5640969023968</v>
       </c>
       <c r="C28" t="n">
-        <v>734.4361027208327</v>
+        <v>734.3561027208326</v>
       </c>
       <c r="D28" t="n">
-        <v>769.5452468458327</v>
+        <v>769.4652468458327</v>
       </c>
       <c r="E28" t="n">
-        <v>809.1641510572457</v>
+        <v>809.0841510572457</v>
       </c>
       <c r="F28" t="n">
-        <v>855.3151236491811</v>
+        <v>855.2351236491811</v>
       </c>
       <c r="G28" t="n">
-        <v>931.1258141262304</v>
+        <v>931.0458141262303</v>
       </c>
       <c r="H28" t="n">
-        <v>1027.892525187267</v>
+        <v>1027.812525187267</v>
       </c>
       <c r="I28" t="n">
-        <v>1189.283805434826</v>
+        <v>1189.203805434826</v>
       </c>
       <c r="J28" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.496154611867</v>
       </c>
       <c r="K28" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.000700024145</v>
       </c>
       <c r="L28" t="n">
-        <v>1608.654647405756</v>
+        <v>1608.574647405756</v>
       </c>
       <c r="M28" t="n">
-        <v>1505.227982468588</v>
+        <v>1505.147982468588</v>
       </c>
       <c r="N28" t="n">
-        <v>1348.401726605486</v>
+        <v>1348.321726605486</v>
       </c>
       <c r="O28" t="n">
-        <v>1114.295626111697</v>
+        <v>1114.215626111697</v>
       </c>
       <c r="P28" t="n">
-        <v>820.7766206439126</v>
+        <v>819.8499076645213</v>
       </c>
       <c r="Q28" t="n">
-        <v>464.3167555675509</v>
+        <v>463.3900425881597</v>
       </c>
       <c r="R28" t="n">
-        <v>82.79157247680381</v>
+        <v>82.71157247680381</v>
       </c>
       <c r="S28" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T28" t="n">
-        <v>164.4096660440508</v>
+        <v>164.3296660440508</v>
       </c>
       <c r="U28" t="n">
-        <v>332.7843563872555</v>
+        <v>332.7043563872555</v>
       </c>
       <c r="V28" t="n">
-        <v>453.3957492732014</v>
+        <v>453.3157492732014</v>
       </c>
       <c r="W28" t="n">
-        <v>547.0766675328789</v>
+        <v>546.9966675328789</v>
       </c>
       <c r="X28" t="n">
-        <v>619.8974585570725</v>
+        <v>619.8174585570724</v>
       </c>
       <c r="Y28" t="n">
-        <v>653.0967592361047</v>
+        <v>653.0167592361047</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>596.6553483293503</v>
+        <v>593.1205880924895</v>
       </c>
       <c r="C29" t="n">
-        <v>466.8830470738009</v>
+        <v>463.34828683694</v>
       </c>
       <c r="D29" t="n">
-        <v>376.6414756194072</v>
+        <v>373.1067153825463</v>
       </c>
       <c r="E29" t="n">
-        <v>292.4361325821661</v>
+        <v>288.9013723453052</v>
       </c>
       <c r="F29" t="n">
-        <v>207.6991338872046</v>
+        <v>204.1643736503437</v>
       </c>
       <c r="G29" t="n">
-        <v>125.5027119537179</v>
+        <v>121.967951716857</v>
       </c>
       <c r="H29" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I29" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J29" t="n">
-        <v>559.4285273090126</v>
+        <v>559.3485273090125</v>
       </c>
       <c r="K29" t="n">
-        <v>733.5813277110226</v>
+        <v>733.5013277110226</v>
       </c>
       <c r="L29" t="n">
-        <v>949.6332762537361</v>
+        <v>949.5532762537362</v>
       </c>
       <c r="M29" t="n">
-        <v>1592.143276253736</v>
+        <v>1591.073276253736</v>
       </c>
       <c r="N29" t="n">
-        <v>2234.653276253736</v>
+        <v>1591.073276253736</v>
       </c>
       <c r="O29" t="n">
-        <v>2395.783377636692</v>
+        <v>1752.203377636691</v>
       </c>
       <c r="P29" t="n">
-        <v>2592.375383975311</v>
+        <v>2393.723377636691</v>
       </c>
       <c r="Q29" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R29" t="n">
-        <v>2596</v>
+        <v>2592.000000000196</v>
       </c>
       <c r="S29" t="n">
-        <v>2451.762030971221</v>
+        <v>2448.22727073436</v>
       </c>
       <c r="T29" t="n">
-        <v>2189.517714621877</v>
+        <v>2185.982954385016</v>
       </c>
       <c r="U29" t="n">
-        <v>1858.092802114017</v>
+        <v>1854.558041877156</v>
       </c>
       <c r="V29" t="n">
-        <v>1546.122070632377</v>
+        <v>1542.587310395516</v>
       </c>
       <c r="W29" t="n">
-        <v>1225.542801964753</v>
+        <v>1222.008041727892</v>
       </c>
       <c r="X29" t="n">
-        <v>951.5207479640785</v>
+        <v>947.9859877272177</v>
       </c>
       <c r="Y29" t="n">
-        <v>759.2809169713448</v>
+        <v>755.746156734484</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>492.6952769985968</v>
+        <v>816.8577012410211</v>
       </c>
       <c r="C30" t="n">
-        <v>127.9478906899915</v>
+        <v>776.3527391748401</v>
       </c>
       <c r="D30" t="n">
-        <v>100.7381059448373</v>
+        <v>424.9005301872616</v>
       </c>
       <c r="E30" t="n">
-        <v>78.84709864997603</v>
+        <v>78.76709864997605</v>
       </c>
       <c r="F30" t="n">
-        <v>60.02261143999941</v>
+        <v>59.94261143999941</v>
       </c>
       <c r="G30" t="n">
-        <v>55.98259997866057</v>
+        <v>55.90259997866057</v>
       </c>
       <c r="H30" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I30" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J30" t="n">
-        <v>245.0840952696386</v>
+        <v>245.0040952696386</v>
       </c>
       <c r="K30" t="n">
-        <v>552.5636804206258</v>
+        <v>552.4836804206258</v>
       </c>
       <c r="L30" t="n">
-        <v>982.9653005063919</v>
+        <v>982.885300506392</v>
       </c>
       <c r="M30" t="n">
-        <v>1254.651042249251</v>
+        <v>1254.571042249251</v>
       </c>
       <c r="N30" t="n">
-        <v>1578.44894421531</v>
+        <v>1578.36894421531</v>
       </c>
       <c r="O30" t="n">
-        <v>1991.777795144312</v>
+        <v>1991.697795144312</v>
       </c>
       <c r="P30" t="n">
-        <v>2244.187340368535</v>
+        <v>2244.107340368535</v>
       </c>
       <c r="Q30" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.107340368535</v>
       </c>
       <c r="R30" t="n">
-        <v>1886.686949702618</v>
+        <v>2061.952218270268</v>
       </c>
       <c r="S30" t="n">
-        <v>1429.292781642309</v>
+        <v>1928.800474452383</v>
       </c>
       <c r="T30" t="n">
-        <v>1347.095458285567</v>
+        <v>1846.603151095642</v>
       </c>
       <c r="U30" t="n">
-        <v>942.8917405937455</v>
+        <v>1766.641857646244</v>
       </c>
       <c r="V30" t="n">
-        <v>848.4365212083716</v>
+        <v>1672.18663826087</v>
       </c>
       <c r="W30" t="n">
-        <v>735.9383970570296</v>
+        <v>1559.688514109528</v>
       </c>
       <c r="X30" t="n">
-        <v>636.0770440818907</v>
+        <v>1284.481892566739</v>
       </c>
       <c r="Y30" t="n">
-        <v>556.8938190655933</v>
+        <v>1205.298667550442</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>686.6440969023969</v>
+        <v>686.5640969023968</v>
       </c>
       <c r="C31" t="n">
-        <v>734.4361027208327</v>
+        <v>734.3561027208326</v>
       </c>
       <c r="D31" t="n">
-        <v>769.5452468458327</v>
+        <v>769.4652468458327</v>
       </c>
       <c r="E31" t="n">
-        <v>809.1641510572457</v>
+        <v>809.0841510572457</v>
       </c>
       <c r="F31" t="n">
-        <v>855.3151236491811</v>
+        <v>855.2351236491811</v>
       </c>
       <c r="G31" t="n">
-        <v>931.1258141262304</v>
+        <v>931.0458141262303</v>
       </c>
       <c r="H31" t="n">
-        <v>1027.892525187267</v>
+        <v>1027.812525187267</v>
       </c>
       <c r="I31" t="n">
-        <v>1189.283805434826</v>
+        <v>1189.203805434826</v>
       </c>
       <c r="J31" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.496154611867</v>
       </c>
       <c r="K31" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.000700024145</v>
       </c>
       <c r="L31" t="n">
-        <v>1609.501360385148</v>
+        <v>1609.421360385147</v>
       </c>
       <c r="M31" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.99469544798</v>
       </c>
       <c r="N31" t="n">
-        <v>1349.248439584877</v>
+        <v>1349.168439584877</v>
       </c>
       <c r="O31" t="n">
-        <v>1115.142339091088</v>
+        <v>1115.062339091088</v>
       </c>
       <c r="P31" t="n">
-        <v>820.7766206439126</v>
+        <v>820.6966206439124</v>
       </c>
       <c r="Q31" t="n">
-        <v>464.3167555675509</v>
+        <v>464.2367555675509</v>
       </c>
       <c r="R31" t="n">
-        <v>82.79157247680381</v>
+        <v>82.71157247680381</v>
       </c>
       <c r="S31" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T31" t="n">
-        <v>164.4096660440508</v>
+        <v>164.3296660440508</v>
       </c>
       <c r="U31" t="n">
-        <v>332.7843563872555</v>
+        <v>332.7043563872555</v>
       </c>
       <c r="V31" t="n">
-        <v>453.3957492732014</v>
+        <v>453.3157492732014</v>
       </c>
       <c r="W31" t="n">
-        <v>547.0766675328789</v>
+        <v>546.9966675328789</v>
       </c>
       <c r="X31" t="n">
-        <v>619.8974585570725</v>
+        <v>619.8174585570724</v>
       </c>
       <c r="Y31" t="n">
-        <v>653.0967592361047</v>
+        <v>653.0167592361047</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>597.1205880922942</v>
+        <v>596.5753483293554</v>
       </c>
       <c r="C32" t="n">
-        <v>467.3482868367447</v>
+        <v>466.803047073806</v>
       </c>
       <c r="D32" t="n">
-        <v>377.106715382351</v>
+        <v>376.5614756194122</v>
       </c>
       <c r="E32" t="n">
-        <v>292.9013723451099</v>
+        <v>292.3561325821712</v>
       </c>
       <c r="F32" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6191338872097</v>
       </c>
       <c r="G32" t="n">
-        <v>125.9679517166617</v>
+        <v>125.4227119537229</v>
       </c>
       <c r="H32" t="n">
-        <v>52.3852397629438</v>
+        <v>51.84000000000508</v>
       </c>
       <c r="I32" t="n">
-        <v>51.92</v>
+        <v>51.84000000000508</v>
       </c>
       <c r="J32" t="n">
-        <v>559.4285273090126</v>
+        <v>559.3485273090176</v>
       </c>
       <c r="K32" t="n">
-        <v>1201.938527309012</v>
+        <v>1200.86852730908</v>
       </c>
       <c r="L32" t="n">
-        <v>1844.448527309012</v>
+        <v>1842.388527309143</v>
       </c>
       <c r="M32" t="n">
-        <v>2238.277892278425</v>
+        <v>1842.388527309143</v>
       </c>
       <c r="N32" t="n">
-        <v>2238.277892278425</v>
+        <v>1842.388527309143</v>
       </c>
       <c r="O32" t="n">
-        <v>2399.40799366138</v>
+        <v>2003.518628692098</v>
       </c>
       <c r="P32" t="n">
-        <v>2596</v>
+        <v>2200.110635030718</v>
       </c>
       <c r="Q32" t="n">
-        <v>2596</v>
+        <v>2592.000000000254</v>
       </c>
       <c r="R32" t="n">
-        <v>2596</v>
+        <v>2592.000000000254</v>
       </c>
       <c r="S32" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.682030971226</v>
       </c>
       <c r="T32" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.437714621882</v>
       </c>
       <c r="U32" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.012802114022</v>
       </c>
       <c r="V32" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.042070632382</v>
       </c>
       <c r="W32" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.462801964758</v>
       </c>
       <c r="X32" t="n">
-        <v>951.9859877270223</v>
+        <v>951.4407479640836</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2009169713499</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>362.0396347695416</v>
+        <v>1141.10012548345</v>
       </c>
       <c r="C33" t="n">
-        <v>321.5346727033605</v>
+        <v>1100.595163417269</v>
       </c>
       <c r="D33" t="n">
-        <v>294.3248879582063</v>
+        <v>749.1429544296908</v>
       </c>
       <c r="E33" t="n">
-        <v>272.4338806633451</v>
+        <v>727.2519471348296</v>
       </c>
       <c r="F33" t="n">
-        <v>253.6093934533685</v>
+        <v>384.1850356824287</v>
       </c>
       <c r="G33" t="n">
-        <v>249.5693819920296</v>
+        <v>380.14502422109</v>
       </c>
       <c r="H33" t="n">
-        <v>245.506782013369</v>
+        <v>51.84000000000508</v>
       </c>
       <c r="I33" t="n">
-        <v>51.92</v>
+        <v>51.84000000000508</v>
       </c>
       <c r="J33" t="n">
-        <v>245.0840952696386</v>
+        <v>245.0040952696436</v>
       </c>
       <c r="K33" t="n">
-        <v>552.5636804206258</v>
+        <v>552.4836804206309</v>
       </c>
       <c r="L33" t="n">
-        <v>982.9653005063919</v>
+        <v>982.885300506397</v>
       </c>
       <c r="M33" t="n">
-        <v>1254.651042249251</v>
+        <v>1254.571042249256</v>
       </c>
       <c r="N33" t="n">
-        <v>1578.44894421531</v>
+        <v>1578.368944215315</v>
       </c>
       <c r="O33" t="n">
-        <v>1991.777795144312</v>
+        <v>1991.697795144317</v>
       </c>
       <c r="P33" t="n">
-        <v>2244.187340368535</v>
+        <v>2244.10734036854</v>
       </c>
       <c r="Q33" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.684564500513</v>
       </c>
       <c r="R33" t="n">
-        <v>1756.031307473563</v>
+        <v>1982.529442402245</v>
       </c>
       <c r="S33" t="n">
-        <v>1622.879563655678</v>
+        <v>1849.377698584361</v>
       </c>
       <c r="T33" t="n">
-        <v>1540.682240298937</v>
+        <v>1767.180375227619</v>
       </c>
       <c r="U33" t="n">
-        <v>1136.478522607115</v>
+        <v>1687.219081778221</v>
       </c>
       <c r="V33" t="n">
-        <v>717.7808789793164</v>
+        <v>1592.763862392847</v>
       </c>
       <c r="W33" t="n">
-        <v>605.2827548279745</v>
+        <v>1480.265738241505</v>
       </c>
       <c r="X33" t="n">
-        <v>505.4214018528356</v>
+        <v>1380.404385266366</v>
       </c>
       <c r="Y33" t="n">
-        <v>426.2381768365382</v>
+        <v>1301.221160250069</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>686.6440969023969</v>
+        <v>686.564096902402</v>
       </c>
       <c r="C34" t="n">
-        <v>734.4361027208327</v>
+        <v>734.3561027208377</v>
       </c>
       <c r="D34" t="n">
-        <v>769.5452468458327</v>
+        <v>769.4652468458378</v>
       </c>
       <c r="E34" t="n">
-        <v>809.1641510572457</v>
+        <v>809.0841510572508</v>
       </c>
       <c r="F34" t="n">
-        <v>855.3151236491811</v>
+        <v>855.2351236491862</v>
       </c>
       <c r="G34" t="n">
-        <v>931.1258141262304</v>
+        <v>931.0458141262354</v>
       </c>
       <c r="H34" t="n">
-        <v>1027.892525187267</v>
+        <v>1027.812525187272</v>
       </c>
       <c r="I34" t="n">
-        <v>1189.283805434826</v>
+        <v>1189.203805434831</v>
       </c>
       <c r="J34" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.496154611872</v>
       </c>
       <c r="K34" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.00070002415</v>
       </c>
       <c r="L34" t="n">
-        <v>1609.501360385148</v>
+        <v>1609.421360385153</v>
       </c>
       <c r="M34" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.994695447985</v>
       </c>
       <c r="N34" t="n">
-        <v>1349.248439584877</v>
+        <v>1349.168439584882</v>
       </c>
       <c r="O34" t="n">
-        <v>1115.142339091088</v>
+        <v>1115.062339091093</v>
       </c>
       <c r="P34" t="n">
-        <v>820.7766206439126</v>
+        <v>820.6966206439176</v>
       </c>
       <c r="Q34" t="n">
-        <v>464.3167555675508</v>
+        <v>464.2367555675559</v>
       </c>
       <c r="R34" t="n">
-        <v>82.79157247680381</v>
+        <v>82.71157247680888</v>
       </c>
       <c r="S34" t="n">
-        <v>51.92</v>
+        <v>51.84000000000508</v>
       </c>
       <c r="T34" t="n">
-        <v>164.4096660440508</v>
+        <v>164.3296660440558</v>
       </c>
       <c r="U34" t="n">
-        <v>332.7843563872555</v>
+        <v>332.7043563872605</v>
       </c>
       <c r="V34" t="n">
-        <v>453.3957492732014</v>
+        <v>453.3157492732065</v>
       </c>
       <c r="W34" t="n">
-        <v>547.0766675328789</v>
+        <v>546.996667532884</v>
       </c>
       <c r="X34" t="n">
-        <v>619.8974585570725</v>
+        <v>619.8174585570775</v>
       </c>
       <c r="Y34" t="n">
-        <v>653.0967592361047</v>
+        <v>653.0167592361098</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>597.1205880922939</v>
+        <v>596.575348329358</v>
       </c>
       <c r="C35" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8030470738086</v>
       </c>
       <c r="D35" t="n">
-        <v>377.1067153823507</v>
+        <v>376.5614756194149</v>
       </c>
       <c r="E35" t="n">
-        <v>292.9013723451097</v>
+        <v>292.3561325821738</v>
       </c>
       <c r="F35" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6191338872123</v>
       </c>
       <c r="G35" t="n">
-        <v>125.9679517166614</v>
+        <v>125.4227119537256</v>
       </c>
       <c r="H35" t="n">
-        <v>51.92</v>
+        <v>51.8400000000077</v>
       </c>
       <c r="I35" t="n">
-        <v>51.92</v>
+        <v>51.8400000000077</v>
       </c>
       <c r="J35" t="n">
-        <v>559.4285273090126</v>
+        <v>133.3468380887251</v>
       </c>
       <c r="K35" t="n">
-        <v>1201.938527309012</v>
+        <v>735.1859437359076</v>
       </c>
       <c r="L35" t="n">
-        <v>1417.990475851726</v>
+        <v>951.2378922786211</v>
       </c>
       <c r="M35" t="n">
-        <v>2060.500475851726</v>
+        <v>1592.757892278715</v>
       </c>
       <c r="N35" t="n">
-        <v>2238.277892278425</v>
+        <v>2234.27789227881</v>
       </c>
       <c r="O35" t="n">
-        <v>2399.40799366138</v>
+        <v>2395.407993661765</v>
       </c>
       <c r="P35" t="n">
-        <v>2596</v>
+        <v>2592.000000000385</v>
       </c>
       <c r="Q35" t="n">
-        <v>2596</v>
+        <v>2592.000000000385</v>
       </c>
       <c r="R35" t="n">
-        <v>2596</v>
+        <v>2592.000000000385</v>
       </c>
       <c r="S35" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.682030971228</v>
       </c>
       <c r="T35" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.437714621885</v>
       </c>
       <c r="U35" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.012802114025</v>
       </c>
       <c r="V35" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.042070632385</v>
       </c>
       <c r="W35" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.462801964761</v>
       </c>
       <c r="X35" t="n">
-        <v>951.9859877270221</v>
+        <v>951.4407479640863</v>
       </c>
       <c r="Y35" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2009169713525</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>992.2829698086708</v>
+        <v>1237.022618183075</v>
       </c>
       <c r="C36" t="n">
-        <v>627.5355835000655</v>
+        <v>1196.517656116894</v>
       </c>
       <c r="D36" t="n">
-        <v>276.0833745124871</v>
+        <v>1169.30787137174</v>
       </c>
       <c r="E36" t="n">
-        <v>254.1923672176258</v>
+        <v>1147.416864076878</v>
       </c>
       <c r="F36" t="n">
-        <v>60.02261143999941</v>
+        <v>804.3499526244775</v>
       </c>
       <c r="G36" t="n">
-        <v>55.98259997866057</v>
+        <v>476.0675169207144</v>
       </c>
       <c r="H36" t="n">
-        <v>51.92</v>
+        <v>245.4267820133767</v>
       </c>
       <c r="I36" t="n">
-        <v>51.92</v>
+        <v>51.8400000000077</v>
       </c>
       <c r="J36" t="n">
-        <v>245.0840952696386</v>
+        <v>245.0040952696463</v>
       </c>
       <c r="K36" t="n">
-        <v>552.5636804206258</v>
+        <v>552.4836804206335</v>
       </c>
       <c r="L36" t="n">
-        <v>982.9653005063919</v>
+        <v>982.8853005063997</v>
       </c>
       <c r="M36" t="n">
-        <v>1254.651042249251</v>
+        <v>1254.571042249259</v>
       </c>
       <c r="N36" t="n">
-        <v>1578.44894421531</v>
+        <v>1578.368944215318</v>
       </c>
       <c r="O36" t="n">
-        <v>1991.777795144312</v>
+        <v>1991.69779514432</v>
       </c>
       <c r="P36" t="n">
-        <v>2244.187340368535</v>
+        <v>2244.107340368543</v>
       </c>
       <c r="Q36" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.684564500516</v>
       </c>
       <c r="R36" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.529442402248</v>
       </c>
       <c r="S36" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.377698584363</v>
       </c>
       <c r="T36" t="n">
-        <v>1846.683151095642</v>
+        <v>1767.180375227622</v>
       </c>
       <c r="U36" t="n">
-        <v>1766.721857646244</v>
+        <v>1687.219081778224</v>
       </c>
       <c r="V36" t="n">
-        <v>1672.26663826087</v>
+        <v>1592.76386239285</v>
       </c>
       <c r="W36" t="n">
-        <v>1559.768514109528</v>
+        <v>1480.265738241508</v>
       </c>
       <c r="X36" t="n">
-        <v>1135.664736891965</v>
+        <v>1380.404385266369</v>
       </c>
       <c r="Y36" t="n">
-        <v>1056.481511875667</v>
+        <v>1301.221160250072</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>686.6440969023969</v>
+        <v>686.5640969024045</v>
       </c>
       <c r="C37" t="n">
-        <v>734.4361027208327</v>
+        <v>734.3561027208402</v>
       </c>
       <c r="D37" t="n">
-        <v>769.5452468458327</v>
+        <v>769.4652468458403</v>
       </c>
       <c r="E37" t="n">
-        <v>809.1641510572457</v>
+        <v>809.0841510572533</v>
       </c>
       <c r="F37" t="n">
-        <v>855.3151236491811</v>
+        <v>855.2351236491887</v>
       </c>
       <c r="G37" t="n">
-        <v>931.1258141262304</v>
+        <v>931.0458141262682</v>
       </c>
       <c r="H37" t="n">
-        <v>1027.892525187267</v>
+        <v>1027.812525187305</v>
       </c>
       <c r="I37" t="n">
-        <v>1189.283805434826</v>
+        <v>1189.203805434863</v>
       </c>
       <c r="J37" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.496154611905</v>
       </c>
       <c r="K37" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.000700024183</v>
       </c>
       <c r="L37" t="n">
-        <v>1608.654647405756</v>
+        <v>1608.574647405794</v>
       </c>
       <c r="M37" t="n">
-        <v>1505.227982468588</v>
+        <v>1505.147982468626</v>
       </c>
       <c r="N37" t="n">
-        <v>1348.401726605486</v>
+        <v>1348.321726605524</v>
       </c>
       <c r="O37" t="n">
-        <v>1114.295626111697</v>
+        <v>1114.215626111735</v>
       </c>
       <c r="P37" t="n">
-        <v>819.9299076645212</v>
+        <v>819.8499076645589</v>
       </c>
       <c r="Q37" t="n">
-        <v>463.4700425881596</v>
+        <v>463.3900425881973</v>
       </c>
       <c r="R37" t="n">
-        <v>81.94485949741255</v>
+        <v>81.86485949745025</v>
       </c>
       <c r="S37" t="n">
-        <v>51.92</v>
+        <v>51.8400000000077</v>
       </c>
       <c r="T37" t="n">
-        <v>164.4096660440508</v>
+        <v>164.3296660440585</v>
       </c>
       <c r="U37" t="n">
-        <v>332.7843563872555</v>
+        <v>332.7043563872631</v>
       </c>
       <c r="V37" t="n">
-        <v>453.3957492732014</v>
+        <v>453.3157492732091</v>
       </c>
       <c r="W37" t="n">
-        <v>547.0766675328789</v>
+        <v>546.9966675328865</v>
       </c>
       <c r="X37" t="n">
-        <v>619.8974585570725</v>
+        <v>619.81745855708</v>
       </c>
       <c r="Y37" t="n">
-        <v>653.0967592361047</v>
+        <v>653.0167592361123</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>597.1205880922939</v>
+        <v>593.1205880927371</v>
       </c>
       <c r="C38" t="n">
-        <v>467.3482868367445</v>
+        <v>463.3482868371876</v>
       </c>
       <c r="D38" t="n">
-        <v>377.1067153823507</v>
+        <v>373.1067153827939</v>
       </c>
       <c r="E38" t="n">
-        <v>292.9013723451097</v>
+        <v>288.9013723455528</v>
       </c>
       <c r="F38" t="n">
-        <v>208.1643736501482</v>
+        <v>204.1643736505914</v>
       </c>
       <c r="G38" t="n">
-        <v>125.9679517166614</v>
+        <v>125.4227119537267</v>
       </c>
       <c r="H38" t="n">
-        <v>51.92</v>
+        <v>51.84000000000886</v>
       </c>
       <c r="I38" t="n">
-        <v>51.92</v>
+        <v>51.84000000000886</v>
       </c>
       <c r="J38" t="n">
-        <v>559.4285273090126</v>
+        <v>559.3485273090214</v>
       </c>
       <c r="K38" t="n">
-        <v>1201.938527309012</v>
+        <v>733.5013277110314</v>
       </c>
       <c r="L38" t="n">
-        <v>1844.448527309012</v>
+        <v>949.553276253745</v>
       </c>
       <c r="M38" t="n">
-        <v>2238.277892278425</v>
+        <v>1591.073276253854</v>
       </c>
       <c r="N38" t="n">
-        <v>2238.277892278425</v>
+        <v>1591.073276253854</v>
       </c>
       <c r="O38" t="n">
-        <v>2399.40799366138</v>
+        <v>1752.203377636809</v>
       </c>
       <c r="P38" t="n">
-        <v>2596</v>
+        <v>2005.555081028177</v>
       </c>
       <c r="Q38" t="n">
-        <v>2596</v>
+        <v>2592.000000000443</v>
       </c>
       <c r="R38" t="n">
-        <v>2596</v>
+        <v>2592.000000000443</v>
       </c>
       <c r="S38" t="n">
-        <v>2452.227270734164</v>
+        <v>2448.227270734607</v>
       </c>
       <c r="T38" t="n">
-        <v>2189.982954384821</v>
+        <v>2185.982954385264</v>
       </c>
       <c r="U38" t="n">
-        <v>1858.558041876961</v>
+        <v>1854.558041877404</v>
       </c>
       <c r="V38" t="n">
-        <v>1546.58731039532</v>
+        <v>1542.587310395764</v>
       </c>
       <c r="W38" t="n">
-        <v>1226.008041727697</v>
+        <v>1222.00804172814</v>
       </c>
       <c r="X38" t="n">
-        <v>951.9859877270221</v>
+        <v>947.9859877274653</v>
       </c>
       <c r="Y38" t="n">
-        <v>759.7461567342884</v>
+        <v>755.7461567347316</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1316.525394051095</v>
+        <v>492.6152769986057</v>
       </c>
       <c r="C39" t="n">
-        <v>1100.675163417264</v>
+        <v>127.8678906900003</v>
       </c>
       <c r="D39" t="n">
-        <v>749.2229544296858</v>
+        <v>100.6581059448461</v>
       </c>
       <c r="E39" t="n">
-        <v>403.0895228924003</v>
+        <v>78.76709864998489</v>
       </c>
       <c r="F39" t="n">
-        <v>60.02261143999941</v>
+        <v>59.94261144000826</v>
       </c>
       <c r="G39" t="n">
-        <v>55.98259997866057</v>
+        <v>55.90259997866944</v>
       </c>
       <c r="H39" t="n">
-        <v>51.92</v>
+        <v>51.84000000000886</v>
       </c>
       <c r="I39" t="n">
-        <v>51.92</v>
+        <v>51.84000000000886</v>
       </c>
       <c r="J39" t="n">
-        <v>245.0840952696386</v>
+        <v>245.0040952696475</v>
       </c>
       <c r="K39" t="n">
-        <v>552.5636804206258</v>
+        <v>552.4836804206346</v>
       </c>
       <c r="L39" t="n">
-        <v>982.9653005063919</v>
+        <v>982.8853005064009</v>
       </c>
       <c r="M39" t="n">
-        <v>1254.651042249251</v>
+        <v>1254.57104224926</v>
       </c>
       <c r="N39" t="n">
-        <v>1578.44894421531</v>
+        <v>1578.368944215319</v>
       </c>
       <c r="O39" t="n">
-        <v>1991.777795144312</v>
+        <v>1991.697795144321</v>
       </c>
       <c r="P39" t="n">
-        <v>2244.187340368535</v>
+        <v>2244.107340368545</v>
       </c>
       <c r="Q39" t="n">
-        <v>2244.187340368535</v>
+        <v>2244.107340368545</v>
       </c>
       <c r="R39" t="n">
-        <v>2062.032218270268</v>
+        <v>2061.952218270277</v>
       </c>
       <c r="S39" t="n">
-        <v>1928.880474452383</v>
+        <v>1928.800474452392</v>
       </c>
       <c r="T39" t="n">
-        <v>1846.683151095642</v>
+        <v>1846.60315109565</v>
       </c>
       <c r="U39" t="n">
-        <v>1766.721857646244</v>
+        <v>1766.641857646253</v>
       </c>
       <c r="V39" t="n">
-        <v>1672.26663826087</v>
+        <v>1672.186638260879</v>
       </c>
       <c r="W39" t="n">
-        <v>1559.768514109528</v>
+        <v>1559.688514109537</v>
       </c>
       <c r="X39" t="n">
-        <v>1459.907161134389</v>
+        <v>1284.481892566748</v>
       </c>
       <c r="Y39" t="n">
-        <v>1380.723936118092</v>
+        <v>881.0562433080265</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>686.6440969023969</v>
+        <v>686.5640969024431</v>
       </c>
       <c r="C40" t="n">
-        <v>734.4361027208327</v>
+        <v>734.3561027208789</v>
       </c>
       <c r="D40" t="n">
-        <v>769.5452468458327</v>
+        <v>769.4652468458789</v>
       </c>
       <c r="E40" t="n">
-        <v>809.1641510572457</v>
+        <v>809.0841510572919</v>
       </c>
       <c r="F40" t="n">
-        <v>855.3151236491811</v>
+        <v>855.2351236492274</v>
       </c>
       <c r="G40" t="n">
-        <v>931.1258141262304</v>
+        <v>931.0458141262766</v>
       </c>
       <c r="H40" t="n">
-        <v>1027.892525187267</v>
+        <v>1027.812525187313</v>
       </c>
       <c r="I40" t="n">
-        <v>1189.283805434826</v>
+        <v>1189.203805434872</v>
       </c>
       <c r="J40" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.496154611913</v>
       </c>
       <c r="K40" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.000700024192</v>
       </c>
       <c r="L40" t="n">
-        <v>1608.654647405756</v>
+        <v>1608.574647405802</v>
       </c>
       <c r="M40" t="n">
-        <v>1505.227982468588</v>
+        <v>1505.147982468635</v>
       </c>
       <c r="N40" t="n">
-        <v>1348.401726605486</v>
+        <v>1348.321726605532</v>
       </c>
       <c r="O40" t="n">
-        <v>1114.295626111697</v>
+        <v>1114.215626111743</v>
       </c>
       <c r="P40" t="n">
-        <v>819.9299076645212</v>
+        <v>819.8499076645676</v>
       </c>
       <c r="Q40" t="n">
-        <v>463.4700425881596</v>
+        <v>463.3900425882059</v>
       </c>
       <c r="R40" t="n">
-        <v>81.94485949741255</v>
+        <v>81.86485949745889</v>
       </c>
       <c r="S40" t="n">
-        <v>51.92</v>
+        <v>51.84000000000886</v>
       </c>
       <c r="T40" t="n">
-        <v>164.4096660440508</v>
+        <v>164.3296660440596</v>
       </c>
       <c r="U40" t="n">
-        <v>332.7843563872555</v>
+        <v>332.7043563872643</v>
       </c>
       <c r="V40" t="n">
-        <v>453.3957492732014</v>
+        <v>453.3157492732103</v>
       </c>
       <c r="W40" t="n">
-        <v>547.0766675328789</v>
+        <v>546.9966675328877</v>
       </c>
       <c r="X40" t="n">
-        <v>619.8974585570725</v>
+        <v>619.8174585570813</v>
       </c>
       <c r="Y40" t="n">
-        <v>653.0967592361047</v>
+        <v>653.016759236151</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>597.1205880922939</v>
+        <v>593.1205880927371</v>
       </c>
       <c r="C41" t="n">
-        <v>467.3482868367445</v>
+        <v>463.3482868371876</v>
       </c>
       <c r="D41" t="n">
-        <v>377.1067153823507</v>
+        <v>373.1067153827939</v>
       </c>
       <c r="E41" t="n">
-        <v>292.9013723451097</v>
+        <v>288.9013723455528</v>
       </c>
       <c r="F41" t="n">
-        <v>208.1643736501482</v>
+        <v>204.1643736505914</v>
       </c>
       <c r="G41" t="n">
-        <v>125.9679517166614</v>
+        <v>125.4227119537267</v>
       </c>
       <c r="H41" t="n">
-        <v>52.38523976294358</v>
+        <v>51.84000000000886</v>
       </c>
       <c r="I41" t="n">
-        <v>51.92</v>
+        <v>51.84000000000886</v>
       </c>
       <c r="J41" t="n">
-        <v>133.4268380887174</v>
+        <v>559.3485273090214</v>
       </c>
       <c r="K41" t="n">
-        <v>307.5796384907274</v>
+        <v>733.5013277110314</v>
       </c>
       <c r="L41" t="n">
-        <v>950.0896384907273</v>
+        <v>949.553276253745</v>
       </c>
       <c r="M41" t="n">
-        <v>1592.599638490728</v>
+        <v>949.553276253745</v>
       </c>
       <c r="N41" t="n">
-        <v>2235.109638490728</v>
+        <v>1167.443074689435</v>
       </c>
       <c r="O41" t="n">
-        <v>2396.239739873683</v>
+        <v>1808.963074689558</v>
       </c>
       <c r="P41" t="n">
-        <v>2592.831746212303</v>
+        <v>2005.555081028177</v>
       </c>
       <c r="Q41" t="n">
-        <v>2596</v>
+        <v>2592.000000000443</v>
       </c>
       <c r="R41" t="n">
-        <v>2596</v>
+        <v>2592.000000000443</v>
       </c>
       <c r="S41" t="n">
-        <v>2452.227270734164</v>
+        <v>2448.227270734607</v>
       </c>
       <c r="T41" t="n">
-        <v>2189.982954384821</v>
+        <v>2185.982954385264</v>
       </c>
       <c r="U41" t="n">
-        <v>1858.558041876961</v>
+        <v>1854.558041877404</v>
       </c>
       <c r="V41" t="n">
-        <v>1546.58731039532</v>
+        <v>1542.587310395764</v>
       </c>
       <c r="W41" t="n">
-        <v>1226.008041727697</v>
+        <v>1222.00804172814</v>
       </c>
       <c r="X41" t="n">
-        <v>951.9859877270221</v>
+        <v>947.9859877274653</v>
       </c>
       <c r="Y41" t="n">
-        <v>759.7461567342884</v>
+        <v>755.7461567347316</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>668.0405455662465</v>
+        <v>816.8577012410299</v>
       </c>
       <c r="C42" t="n">
-        <v>627.5355835000654</v>
+        <v>776.3527391748488</v>
       </c>
       <c r="D42" t="n">
-        <v>600.3257987549113</v>
+        <v>749.1429544296947</v>
       </c>
       <c r="E42" t="n">
-        <v>578.4347914600501</v>
+        <v>403.0095228924092</v>
       </c>
       <c r="F42" t="n">
-        <v>559.6103042500735</v>
+        <v>59.94261144000826</v>
       </c>
       <c r="G42" t="n">
-        <v>380.2250242210849</v>
+        <v>55.90259997866944</v>
       </c>
       <c r="H42" t="n">
-        <v>51.92</v>
+        <v>51.84000000000886</v>
       </c>
       <c r="I42" t="n">
-        <v>51.92</v>
+        <v>51.84000000000886</v>
       </c>
       <c r="J42" t="n">
-        <v>245.0840952696386</v>
+        <v>245.0040952696475</v>
       </c>
       <c r="K42" t="n">
-        <v>552.5636804206258</v>
+        <v>552.4836804206346</v>
       </c>
       <c r="L42" t="n">
-        <v>982.9653005063919</v>
+        <v>982.8853005064009</v>
       </c>
       <c r="M42" t="n">
-        <v>1254.651042249251</v>
+        <v>1254.57104224926</v>
       </c>
       <c r="N42" t="n">
-        <v>1578.44894421531</v>
+        <v>1578.368944215319</v>
       </c>
       <c r="O42" t="n">
-        <v>1991.777795144312</v>
+        <v>1991.697795144321</v>
       </c>
       <c r="P42" t="n">
-        <v>2244.187340368535</v>
+        <v>2244.107340368545</v>
       </c>
       <c r="Q42" t="n">
-        <v>2244.187340368535</v>
+        <v>2244.107340368545</v>
       </c>
       <c r="R42" t="n">
-        <v>2062.032218270268</v>
+        <v>2061.952218270277</v>
       </c>
       <c r="S42" t="n">
-        <v>1928.880474452383</v>
+        <v>1928.800474452392</v>
       </c>
       <c r="T42" t="n">
-        <v>1846.683151095642</v>
+        <v>1671.257882528001</v>
       </c>
       <c r="U42" t="n">
-        <v>1766.721857646244</v>
+        <v>1267.054164836179</v>
       </c>
       <c r="V42" t="n">
-        <v>1348.024214018445</v>
+        <v>1172.598945450805</v>
       </c>
       <c r="W42" t="n">
-        <v>911.2836656246793</v>
+        <v>1060.100821299463</v>
       </c>
       <c r="X42" t="n">
-        <v>811.4223126495403</v>
+        <v>960.2394683243238</v>
       </c>
       <c r="Y42" t="n">
-        <v>732.239087633243</v>
+        <v>881.0562433080264</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>686.6440969023969</v>
+        <v>686.5640969024057</v>
       </c>
       <c r="C43" t="n">
-        <v>734.4361027208327</v>
+        <v>734.3561027208415</v>
       </c>
       <c r="D43" t="n">
-        <v>769.5452468458327</v>
+        <v>769.4652468458415</v>
       </c>
       <c r="E43" t="n">
-        <v>809.1641510572457</v>
+        <v>809.0841510572545</v>
       </c>
       <c r="F43" t="n">
-        <v>855.3151236491811</v>
+        <v>855.23512364919</v>
       </c>
       <c r="G43" t="n">
-        <v>931.1258141262304</v>
+        <v>931.0458141262392</v>
       </c>
       <c r="H43" t="n">
-        <v>1027.892525187267</v>
+        <v>1027.812525187276</v>
       </c>
       <c r="I43" t="n">
-        <v>1189.283805434826</v>
+        <v>1189.203805434835</v>
       </c>
       <c r="J43" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.49615461195</v>
       </c>
       <c r="K43" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.000700024229</v>
       </c>
       <c r="L43" t="n">
-        <v>1608.654647405756</v>
+        <v>1608.574647405839</v>
       </c>
       <c r="M43" t="n">
-        <v>1505.227982468588</v>
+        <v>1505.147982468672</v>
       </c>
       <c r="N43" t="n">
-        <v>1348.401726605486</v>
+        <v>1348.321726605569</v>
       </c>
       <c r="O43" t="n">
-        <v>1114.295626111697</v>
+        <v>1114.21562611178</v>
       </c>
       <c r="P43" t="n">
-        <v>819.9299076645212</v>
+        <v>819.8499076646044</v>
       </c>
       <c r="Q43" t="n">
-        <v>463.4700425881596</v>
+        <v>463.3900425882427</v>
       </c>
       <c r="R43" t="n">
-        <v>81.94485949741255</v>
+        <v>81.86485949749573</v>
       </c>
       <c r="S43" t="n">
-        <v>51.92</v>
+        <v>51.84000000000886</v>
       </c>
       <c r="T43" t="n">
-        <v>164.4096660440508</v>
+        <v>164.3296660440596</v>
       </c>
       <c r="U43" t="n">
-        <v>332.7843563872555</v>
+        <v>332.7043563872643</v>
       </c>
       <c r="V43" t="n">
-        <v>453.3957492732014</v>
+        <v>453.3157492732103</v>
       </c>
       <c r="W43" t="n">
-        <v>547.0766675328789</v>
+        <v>546.9966675328877</v>
       </c>
       <c r="X43" t="n">
-        <v>619.8974585570725</v>
+        <v>619.8174585570813</v>
       </c>
       <c r="Y43" t="n">
-        <v>653.0967592361047</v>
+        <v>653.0167592361136</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>596.6553483293503</v>
+        <v>593.1205880927369</v>
       </c>
       <c r="C44" t="n">
-        <v>466.8830470738009</v>
+        <v>463.3482868371874</v>
       </c>
       <c r="D44" t="n">
-        <v>376.6414756194072</v>
+        <v>373.1067153827937</v>
       </c>
       <c r="E44" t="n">
-        <v>292.4361325821661</v>
+        <v>288.9013723455526</v>
       </c>
       <c r="F44" t="n">
-        <v>207.6991338872047</v>
+        <v>204.1643736505911</v>
       </c>
       <c r="G44" t="n">
-        <v>125.5027119537179</v>
+        <v>125.4227119537267</v>
       </c>
       <c r="H44" t="n">
-        <v>51.92</v>
+        <v>51.84000000000886</v>
       </c>
       <c r="I44" t="n">
-        <v>51.92</v>
+        <v>51.84000000000886</v>
       </c>
       <c r="J44" t="n">
-        <v>133.4268380887174</v>
+        <v>559.3485273090214</v>
       </c>
       <c r="K44" t="n">
-        <v>307.5796384907274</v>
+        <v>733.5013277110314</v>
       </c>
       <c r="L44" t="n">
-        <v>950.0896384907273</v>
+        <v>949.553276253745</v>
       </c>
       <c r="M44" t="n">
-        <v>1592.599638490728</v>
+        <v>1591.073276253897</v>
       </c>
       <c r="N44" t="n">
-        <v>2235.109638490728</v>
+        <v>1591.073276253897</v>
       </c>
       <c r="O44" t="n">
-        <v>2396.239739873683</v>
+        <v>1752.203377636852</v>
       </c>
       <c r="P44" t="n">
-        <v>2592.831746212303</v>
+        <v>2005.555081028177</v>
       </c>
       <c r="Q44" t="n">
-        <v>2596</v>
+        <v>2592.000000000443</v>
       </c>
       <c r="R44" t="n">
-        <v>2596</v>
+        <v>2592.000000000443</v>
       </c>
       <c r="S44" t="n">
-        <v>2451.762030971221</v>
+        <v>2448.227270734607</v>
       </c>
       <c r="T44" t="n">
-        <v>2189.517714621877</v>
+        <v>2185.982954385264</v>
       </c>
       <c r="U44" t="n">
-        <v>1858.092802114017</v>
+        <v>1854.558041877404</v>
       </c>
       <c r="V44" t="n">
-        <v>1546.122070632377</v>
+        <v>1542.587310395763</v>
       </c>
       <c r="W44" t="n">
-        <v>1225.542801964753</v>
+        <v>1222.008041728139</v>
       </c>
       <c r="X44" t="n">
-        <v>951.5207479640785</v>
+        <v>947.985987727465</v>
       </c>
       <c r="Y44" t="n">
-        <v>759.2809169713448</v>
+        <v>755.7461567347314</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>992.2829698086706</v>
+        <v>1237.022618183076</v>
       </c>
       <c r="C45" t="n">
-        <v>627.5355835000653</v>
+        <v>1100.595163417273</v>
       </c>
       <c r="D45" t="n">
-        <v>424.9805301872615</v>
+        <v>749.1429544296947</v>
       </c>
       <c r="E45" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0095228924092</v>
       </c>
       <c r="F45" t="n">
-        <v>60.0226114399994</v>
+        <v>59.94261144000826</v>
       </c>
       <c r="G45" t="n">
-        <v>55.98259997866058</v>
+        <v>55.90259997866942</v>
       </c>
       <c r="H45" t="n">
-        <v>51.92</v>
+        <v>51.84000000000886</v>
       </c>
       <c r="I45" t="n">
-        <v>51.92</v>
+        <v>51.84000000000886</v>
       </c>
       <c r="J45" t="n">
-        <v>245.0840952696386</v>
+        <v>245.0040952696475</v>
       </c>
       <c r="K45" t="n">
-        <v>552.5636804206258</v>
+        <v>552.4836804206346</v>
       </c>
       <c r="L45" t="n">
-        <v>982.9653005063919</v>
+        <v>982.8853005064009</v>
       </c>
       <c r="M45" t="n">
-        <v>1254.651042249251</v>
+        <v>1254.57104224926</v>
       </c>
       <c r="N45" t="n">
-        <v>1578.44894421531</v>
+        <v>1578.368944215319</v>
       </c>
       <c r="O45" t="n">
-        <v>1991.777795144312</v>
+        <v>1991.697795144321</v>
       </c>
       <c r="P45" t="n">
-        <v>2244.187340368535</v>
+        <v>2244.107340368545</v>
       </c>
       <c r="Q45" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.684564500517</v>
       </c>
       <c r="R45" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.529442402249</v>
       </c>
       <c r="S45" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.377698584365</v>
       </c>
       <c r="T45" t="n">
-        <v>1846.683151095641</v>
+        <v>1767.180375227623</v>
       </c>
       <c r="U45" t="n">
-        <v>1766.721857646244</v>
+        <v>1687.219081778225</v>
       </c>
       <c r="V45" t="n">
-        <v>1348.024214018445</v>
+        <v>1592.763862392851</v>
       </c>
       <c r="W45" t="n">
-        <v>1235.526089867103</v>
+        <v>1480.265738241509</v>
       </c>
       <c r="X45" t="n">
-        <v>1135.664736891964</v>
+        <v>1380.40438526637</v>
       </c>
       <c r="Y45" t="n">
-        <v>1056.481511875667</v>
+        <v>1301.221160250073</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>686.6440969023969</v>
+        <v>686.5640969024926</v>
       </c>
       <c r="C46" t="n">
-        <v>734.4361027208327</v>
+        <v>734.3561027209283</v>
       </c>
       <c r="D46" t="n">
-        <v>769.5452468458327</v>
+        <v>769.4652468459284</v>
       </c>
       <c r="E46" t="n">
-        <v>809.1641510572457</v>
+        <v>809.0841510573414</v>
       </c>
       <c r="F46" t="n">
-        <v>855.3151236491811</v>
+        <v>855.2351236492768</v>
       </c>
       <c r="G46" t="n">
-        <v>931.1258141262304</v>
+        <v>931.045814126326</v>
       </c>
       <c r="H46" t="n">
-        <v>1027.892525187267</v>
+        <v>1027.812525187363</v>
       </c>
       <c r="I46" t="n">
-        <v>1189.283805434826</v>
+        <v>1189.203805434921</v>
       </c>
       <c r="J46" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.496154611963</v>
       </c>
       <c r="K46" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.000700024241</v>
       </c>
       <c r="L46" t="n">
-        <v>1608.654647405756</v>
+        <v>1608.574647405852</v>
       </c>
       <c r="M46" t="n">
-        <v>1505.227982468588</v>
+        <v>1505.147982468684</v>
       </c>
       <c r="N46" t="n">
-        <v>1348.401726605486</v>
+        <v>1348.321726605582</v>
       </c>
       <c r="O46" t="n">
-        <v>1114.295626111697</v>
+        <v>1114.215626111793</v>
       </c>
       <c r="P46" t="n">
-        <v>819.9299076645211</v>
+        <v>819.8499076646173</v>
       </c>
       <c r="Q46" t="n">
-        <v>463.4700425881595</v>
+        <v>463.3900425882557</v>
       </c>
       <c r="R46" t="n">
-        <v>81.94485949741244</v>
+        <v>81.86485949750858</v>
       </c>
       <c r="S46" t="n">
-        <v>51.92</v>
+        <v>51.84000000000886</v>
       </c>
       <c r="T46" t="n">
-        <v>164.4096660440508</v>
+        <v>164.3296660440596</v>
       </c>
       <c r="U46" t="n">
-        <v>332.7843563872555</v>
+        <v>332.7043563872643</v>
       </c>
       <c r="V46" t="n">
-        <v>453.3957492732014</v>
+        <v>453.3157492732103</v>
       </c>
       <c r="W46" t="n">
-        <v>547.0766675328789</v>
+        <v>546.9966675329746</v>
       </c>
       <c r="X46" t="n">
-        <v>619.8974585570725</v>
+        <v>619.8174585571682</v>
       </c>
       <c r="Y46" t="n">
-        <v>653.0967592361047</v>
+        <v>653.0167592362004</v>
       </c>
     </row>
   </sheetData>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2405037325275146</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>846.2608914614127</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N2" t="n">
-        <v>778.0826666125488</v>
+        <v>777.3653500296342</v>
       </c>
       <c r="O2" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P2" t="n">
-        <v>315.3213213472141</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>370.5618244726559</v>
+        <v>362.2957550800353</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2405037325275146</v>
+        <v>373.8993027275024</v>
       </c>
       <c r="K5" t="n">
-        <v>321.8400703517588</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>846.2608914614127</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N5" t="n">
-        <v>778.0826666125488</v>
+        <v>637.6540577531742</v>
       </c>
       <c r="O5" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>364.0430754681111</v>
+        <v>128.1077446289929</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>374.2405037325275</v>
+        <v>373.8993027275024</v>
       </c>
       <c r="K8" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>707.7620966723902</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N8" t="n">
-        <v>404.0826666125488</v>
+        <v>584.9827562456367</v>
       </c>
       <c r="O8" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>502.5418702571336</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,19 +8675,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>433.9659648939233</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M11" t="n">
-        <v>950.4344291498551</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N11" t="n">
-        <v>879.4920535472222</v>
+        <v>628.2994929102651</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8918,22 +8918,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N14" t="n">
-        <v>879.4920535472222</v>
+        <v>234.8470915832563</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>26.68372459829277</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>430.7657085427137</v>
       </c>
       <c r="M17" t="n">
-        <v>950.4344291498551</v>
+        <v>523.3299489149077</v>
       </c>
       <c r="N17" t="n">
-        <v>721.0894134186553</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,13 +9389,13 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L20" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>950.4344291498551</v>
+        <v>318.9437086192779</v>
       </c>
       <c r="N20" t="n">
         <v>879.4920535472222</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>26.68372459829277</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,7 +9623,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -9635,16 +9635,16 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N23" t="n">
-        <v>879.4920535472222</v>
+        <v>270.6671975990795</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q23" t="n">
-        <v>27.14469655484982</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,16 +9863,16 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>433.9659648939233</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>950.4344291498551</v>
+        <v>789.0721930616919</v>
       </c>
       <c r="N26" t="n">
-        <v>879.4920535472222</v>
+        <v>878.4920535472222</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10106,19 +10106,19 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>950.4344291498551</v>
+        <v>949.4344291498551</v>
       </c>
       <c r="N29" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>449.422215819576</v>
       </c>
       <c r="Q29" t="n">
-        <v>27.14469655484982</v>
+        <v>223.7628847756783</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,13 +10337,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>473.08808040201</v>
+        <v>472.0880804020735</v>
       </c>
       <c r="L32" t="n">
-        <v>430.7657085427136</v>
+        <v>429.765708542777</v>
       </c>
       <c r="M32" t="n">
-        <v>699.241868512898</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N32" t="n">
         <v>230.4920535472222</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>23.48346824708341</v>
+        <v>419.3313116506547</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,19 +10571,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>473.08808040201</v>
+        <v>432.0063689345177</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>950.4344291498551</v>
+        <v>949.4344291499501</v>
       </c>
       <c r="N35" t="n">
-        <v>410.0652014529786</v>
+        <v>878.4920535473175</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10811,13 +10811,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>473.08808040201</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>699.241868512898</v>
+        <v>949.4344291499647</v>
       </c>
       <c r="N38" t="n">
         <v>230.4920535472222</v>
@@ -10826,10 +10826,10 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>57.33302732600905</v>
       </c>
       <c r="Q38" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,28 +11045,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>950.4344291498551</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N41" t="n">
-        <v>879.4920535472222</v>
+        <v>450.5827590378176</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>485.2423218355233</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>26.68372459829277</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,28 +11282,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>950.4344291498551</v>
+        <v>949.4344291500083</v>
       </c>
       <c r="N44" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>57.33302732596539</v>
       </c>
       <c r="Q44" t="n">
-        <v>26.68372459829277</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>5.067057884389214e-13</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -23414,7 +23414,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -23432,7 +23432,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23648,13 +23648,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8382458495976817</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.8382458495976266</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -23888,7 +23888,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8382458495977119</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -23906,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24459,7 +24459,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.420212634686095</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -24608,13 +24608,13 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0.8382458495973992</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>0.8382458495972855</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -24663,7 +24663,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>3.420212634492273</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.8382458495976959</v>
+        <v>0.8382458495972447</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -24933,7 +24933,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.420212634439366</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -25170,7 +25170,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.420212634312406</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -25328,7 +25328,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495676417</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25371,7 +25371,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>3.420212634255904</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -25565,7 +25565,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495602343</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25608,7 +25608,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>3.420212634255904</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495237657</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25845,7 +25845,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>3.420212634256119</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -26039,7 +26039,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.8382458495974596</v>
+        <v>0.838245849511047</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>797725.6530297217</v>
+        <v>797643.2715297217</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1521867.451220963</v>
+        <v>1521785.069720963</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2246009.249412206</v>
+        <v>2245926.867912206</v>
       </c>
     </row>
     <row r="5">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6590356.308803302</v>
+        <v>6590128.849307377</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7314486.539201817</v>
+        <v>7314102.53657361</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8038616.769600337</v>
+        <v>8038076.223839857</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8762746.999998862</v>
+        <v>8762049.91110611</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9486877.230397385</v>
+        <v>9486023.598372364</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10211007.46079591</v>
+        <v>10209997.28563862</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10935137.69119443</v>
+        <v>10933970.97290487</v>
       </c>
     </row>
   </sheetData>
@@ -26278,7 +26278,7 @@
         <v>1479768.022390799</v>
       </c>
       <c r="E2" t="n">
-        <v>1479744.383857841</v>
+        <v>1479744.383857839</v>
       </c>
       <c r="F2" t="n">
         <v>1479744.38385784</v>
@@ -26290,28 +26290,28 @@
         <v>1479744.383857841</v>
       </c>
       <c r="I2" t="n">
-        <v>1479744.383857841</v>
+        <v>1479744.38385784</v>
       </c>
       <c r="J2" t="n">
-        <v>1479744.38385784</v>
+        <v>1479424.491370119</v>
       </c>
       <c r="K2" t="n">
-        <v>1479744.383857841</v>
+        <v>1479424.491370137</v>
       </c>
       <c r="L2" t="n">
-        <v>1479744.38385784</v>
+        <v>1479424.491370141</v>
       </c>
       <c r="M2" t="n">
-        <v>1479744.38385784</v>
+        <v>1479424.491370153</v>
       </c>
       <c r="N2" t="n">
-        <v>1479744.38385784</v>
+        <v>1479424.491370159</v>
       </c>
       <c r="O2" t="n">
-        <v>1479744.383857841</v>
+        <v>1479424.491370161</v>
       </c>
       <c r="P2" t="n">
-        <v>1479744.383857839</v>
+        <v>1479424.491370161</v>
       </c>
     </row>
     <row r="3">
@@ -26321,7 +26321,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>231098</v>
+        <v>232073</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26330,7 +26330,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>589550</v>
+        <v>588575</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,19 +26345,19 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>388448</v>
+        <v>388096</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.232991391792893e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>96800</v>
+        <v>96800.00000001153</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>5.122274160385132e-09</v>
       </c>
       <c r="O3" t="n">
         <v>256800</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577464.9346667652</v>
+        <v>570746.4673071974</v>
       </c>
       <c r="C4" t="n">
-        <v>575456.0124792766</v>
+        <v>568738.1032495913</v>
       </c>
       <c r="D4" t="n">
-        <v>573444.3650634525</v>
+        <v>566727.0147207876</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.979796175</v>
+        <v>483475.9886658207</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779521</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562991</v>
+        <v>480101.5363259448</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463364</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457892</v>
+        <v>476717.7102154349</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308645</v>
+        <v>474974.8741081326</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473276.9235466269</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471576.5605205692</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497193</v>
+        <v>469873.7672149726</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589554</v>
+        <v>468168.5255757506</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604933</v>
+        <v>466460.8173050839</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.4934089099</v>
+        <v>464750.6238566192</v>
       </c>
     </row>
     <row r="5">
@@ -26425,13 +26425,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="C5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="D5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="E5" t="n">
         <v>73944.549</v>
@@ -26449,25 +26449,25 @@
         <v>73944.549</v>
       </c>
       <c r="J5" t="n">
-        <v>73944.549</v>
+        <v>73883.74900000001</v>
       </c>
       <c r="K5" t="n">
-        <v>73944.549</v>
+        <v>73883.74900000001</v>
       </c>
       <c r="L5" t="n">
-        <v>73944.549</v>
+        <v>73883.74900000385</v>
       </c>
       <c r="M5" t="n">
-        <v>73944.549</v>
+        <v>73883.74900000585</v>
       </c>
       <c r="N5" t="n">
-        <v>73944.549</v>
+        <v>73883.74900000673</v>
       </c>
       <c r="O5" t="n">
-        <v>73944.549</v>
+        <v>73883.74900000673</v>
       </c>
       <c r="P5" t="n">
-        <v>73944.549</v>
+        <v>73883.74900000673</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>612614.6877240342</v>
+        <v>618336.3550836018</v>
       </c>
       <c r="C6" t="n">
-        <v>845721.6099115222</v>
+        <v>852417.7191412081</v>
       </c>
       <c r="D6" t="n">
-        <v>847733.2573273466</v>
+        <v>854428.8076700118</v>
       </c>
       <c r="E6" t="n">
-        <v>326310.8550616657</v>
+        <v>333748.8461920186</v>
       </c>
       <c r="F6" t="n">
-        <v>917546.9178798874</v>
+        <v>924009.9090102421</v>
       </c>
       <c r="G6" t="n">
-        <v>919235.3074015407</v>
+        <v>925698.2985318952</v>
       </c>
       <c r="H6" t="n">
-        <v>920926.0403115043</v>
+        <v>927389.0314418585</v>
       </c>
       <c r="I6" t="n">
-        <v>922619.1335120514</v>
+        <v>929082.1246424048</v>
       </c>
       <c r="J6" t="n">
-        <v>535866.604126976</v>
+        <v>542469.8682619862</v>
       </c>
       <c r="K6" t="n">
-        <v>926012.4695058099</v>
+        <v>932263.8188235096</v>
       </c>
       <c r="L6" t="n">
-        <v>927712.7472281525</v>
+        <v>933964.1818495451</v>
       </c>
       <c r="M6" t="n">
-        <v>832615.4551081212</v>
+        <v>838866.9751551634</v>
       </c>
       <c r="N6" t="n">
-        <v>931120.6111988848</v>
+        <v>937372.2167943965</v>
       </c>
       <c r="O6" t="n">
-        <v>676028.2337973473</v>
+        <v>682279.92506507</v>
       </c>
       <c r="P6" t="n">
-        <v>934538.3414489294</v>
+        <v>940790.1185135351</v>
       </c>
     </row>
   </sheetData>
@@ -26807,13 +26807,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E3" t="n">
         <v>344</v>
@@ -26883,25 +26883,25 @@
         <v>649</v>
       </c>
       <c r="J4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="K4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="L4" t="n">
-        <v>649</v>
+        <v>648.0000000000634</v>
       </c>
       <c r="M4" t="n">
-        <v>649</v>
+        <v>648.0000000000962</v>
       </c>
       <c r="N4" t="n">
-        <v>649</v>
+        <v>648.0000000001107</v>
       </c>
       <c r="O4" t="n">
-        <v>649</v>
+        <v>648.0000000001107</v>
       </c>
       <c r="P4" t="n">
-        <v>649</v>
+        <v>648.0000000001107</v>
       </c>
     </row>
   </sheetData>
@@ -26984,16 +26984,16 @@
         <v>321</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>321</v>
@@ -27008,7 +27008,7 @@
         <v>-0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>321</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27033,7 +27033,7 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
@@ -27100,19 +27100,19 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>5.633498272138901e-11</v>
       </c>
       <c r="M4" t="n">
-        <v>275</v>
+        <v>275.0000000000256</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>7.449642501094125e-12</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>132.4740095033003</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>225.120779732817</v>
+        <v>222.914845633834</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27518,22 +27518,22 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>307.1082651984977</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27566,10 +27566,10 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>68.24613196914004</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>26.1959257979226</v>
+        <v>400</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27600,28 +27600,28 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>349.8196762707121</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>244.8599384153005</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>171.1020457840527</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>396.2647849014816</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K4" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
-        <v>396.2015953708939</v>
+        <v>400</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27642,7 +27642,7 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>359.1680042930194</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
         <v>400</v>
@@ -27651,16 +27651,16 @@
         <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>317.1679785220395</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>134.2726973711268</v>
+        <v>132.1643059857123</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,10 +27718,10 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S5" t="n">
-        <v>398.2013121321733</v>
+        <v>400</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27755,7 +27755,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -27764,13 +27764,13 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0491815260438</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I6" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27797,7 +27797,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>394.6389026985112</v>
+        <v>252.7589796949874</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
@@ -27843,22 +27843,22 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>244.8599384153005</v>
+        <v>244.858135136612</v>
       </c>
       <c r="H7" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>175.9447529565927</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K7" t="n">
         <v>400</v>
       </c>
       <c r="L7" t="n">
-        <v>396.2015953708939</v>
+        <v>400</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27891,7 +27891,7 @@
         <v>400</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>375.1409003843276</v>
       </c>
       <c r="X7" t="n">
         <v>247.4436454301076</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>134.2726973711268</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,10 +27955,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S8" t="n">
-        <v>398.2013121321733</v>
+        <v>398.0465935392085</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27989,25 +27989,25 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>207.4990601318526</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0491815260438</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I9" t="n">
-        <v>209.5726123064429</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,16 +28031,16 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R9" t="n">
-        <v>159.6519859716246</v>
+        <v>400</v>
       </c>
       <c r="S9" t="n">
-        <v>88.48881128536601</v>
+        <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>264.1897658817312</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28065,37 +28065,37 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>351.0666720113006</v>
+      </c>
+      <c r="C10" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D10" t="n">
         <v>400</v>
       </c>
-      <c r="C10" t="n">
-        <v>331.9879303441195</v>
-      </c>
-      <c r="D10" t="n">
-        <v>285.5362180555555</v>
-      </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
-        <v>244.8599384153005</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>171.1020457840527</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>22.26478490148153</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K10" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L10" t="n">
-        <v>396.2015953708939</v>
+        <v>400</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28116,19 +28116,19 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>359.1680042930194</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
         <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
@@ -28195,13 +28195,13 @@
         <v>164.009091290606</v>
       </c>
       <c r="S11" t="n">
-        <v>320.539412634686</v>
+        <v>321</v>
       </c>
       <c r="T11" t="n">
         <v>321</v>
       </c>
       <c r="U11" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="V11" t="n">
         <v>321</v>
@@ -28223,11 +28223,11 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
         <v>147.4081841180269</v>
       </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
@@ -28235,7 +28235,7 @@
         <v>321</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G12" t="n">
         <v>321</v>
@@ -28271,7 +28271,7 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>321</v>
@@ -28460,10 +28460,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C15" t="n">
-        <v>226.0367322273743</v>
+        <v>321</v>
       </c>
       <c r="D15" t="n">
         <v>321</v>
@@ -28475,7 +28475,7 @@
         <v>321</v>
       </c>
       <c r="G15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>321</v>
@@ -28505,13 +28505,13 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>321</v>
+        <v>147.4081841180268</v>
       </c>
       <c r="T15" t="n">
         <v>321</v>
@@ -28529,7 +28529,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16">
@@ -28636,10 +28636,10 @@
         <v>321</v>
       </c>
       <c r="H17" t="n">
-        <v>321</v>
+        <v>320.5394126346856</v>
       </c>
       <c r="I17" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28697,19 +28697,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G18" t="n">
         <v>321</v>
@@ -28742,13 +28742,13 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>321</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="T18" t="n">
         <v>321</v>
@@ -28760,7 +28760,7 @@
         <v>321</v>
       </c>
       <c r="W18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>321</v>
@@ -28876,7 +28876,7 @@
         <v>321</v>
       </c>
       <c r="I20" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28906,7 +28906,7 @@
         <v>164.009091290606</v>
       </c>
       <c r="S20" t="n">
-        <v>320.539412634686</v>
+        <v>321</v>
       </c>
       <c r="T20" t="n">
         <v>321</v>
@@ -28940,19 +28940,19 @@
         <v>321</v>
       </c>
       <c r="D21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>226.0367322273742</v>
+        <v>226.0367322273743</v>
       </c>
       <c r="I21" t="n">
         <v>191.6509141932353</v>
@@ -28994,7 +28994,7 @@
         <v>321</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W21" t="n">
         <v>321</v>
@@ -29110,7 +29110,7 @@
         <v>321</v>
       </c>
       <c r="H23" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I23" t="n">
         <v>96.76634561233286</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S23" t="n">
         <v>321</v>
@@ -29171,13 +29171,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E24" t="n">
         <v>321</v>
@@ -29219,19 +29219,19 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R24" t="n">
-        <v>321</v>
+        <v>147.4081841180267</v>
       </c>
       <c r="S24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
         <v>321</v>
       </c>
       <c r="U24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>321</v>
@@ -29240,7 +29240,7 @@
         <v>321</v>
       </c>
       <c r="Y24" t="n">
-        <v>147.408184118027</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25">
@@ -29347,7 +29347,7 @@
         <v>321</v>
       </c>
       <c r="H26" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I26" t="n">
         <v>96.76634561233286</v>
@@ -29408,16 +29408,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E27" t="n">
-        <v>96.68764642060958</v>
+        <v>321</v>
       </c>
       <c r="F27" t="n">
         <v>321</v>
@@ -29429,7 +29429,7 @@
         <v>321</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29465,7 +29465,7 @@
         <v>321</v>
       </c>
       <c r="U27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>321</v>
@@ -29477,7 +29477,7 @@
         <v>321</v>
       </c>
       <c r="Y27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -29614,10 +29614,10 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>164.009091290606</v>
+        <v>164.0090912908035</v>
       </c>
       <c r="S29" t="n">
-        <v>320.539412634686</v>
+        <v>321</v>
       </c>
       <c r="T29" t="n">
         <v>321</v>
@@ -29645,16 +29645,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>321</v>
@@ -29690,19 +29690,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R30" t="n">
-        <v>226.0367322273741</v>
+        <v>321</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T30" t="n">
         <v>321</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V30" t="n">
         <v>321</v>
@@ -29711,7 +29711,7 @@
         <v>321</v>
       </c>
       <c r="X30" t="n">
-        <v>321</v>
+        <v>147.4081841180267</v>
       </c>
       <c r="Y30" t="n">
         <v>321</v>
@@ -29824,7 +29824,7 @@
         <v>321</v>
       </c>
       <c r="I32" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29882,28 +29882,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>321</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="C33" t="n">
         <v>321</v>
       </c>
       <c r="D33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>321</v>
       </c>
       <c r="F33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>321</v>
       </c>
       <c r="H33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29927,10 +29927,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>18.05909831126223</v>
+        <v>321</v>
       </c>
       <c r="S33" t="n">
         <v>321</v>
@@ -29939,10 +29939,10 @@
         <v>321</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W33" t="n">
         <v>321</v>
@@ -30058,7 +30058,7 @@
         <v>321</v>
       </c>
       <c r="H35" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I35" t="n">
         <v>96.76634561233286</v>
@@ -30122,25 +30122,25 @@
         <v>321</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E36" t="n">
         <v>321</v>
       </c>
       <c r="F36" t="n">
-        <v>147.4081841180267</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>321</v>
+        <v>96.68764642060967</v>
       </c>
       <c r="I36" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30164,7 +30164,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>321</v>
@@ -30185,7 +30185,7 @@
         <v>321</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y36" t="n">
         <v>321</v>
@@ -30213,7 +30213,7 @@
         <v>321</v>
       </c>
       <c r="G37" t="n">
-        <v>321</v>
+        <v>321.0000000000305</v>
       </c>
       <c r="H37" t="n">
         <v>321</v>
@@ -30295,7 +30295,7 @@
         <v>321</v>
       </c>
       <c r="H38" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I38" t="n">
         <v>96.76634561233286</v>
@@ -30356,19 +30356,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>147.4081841180269</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G39" t="n">
         <v>321</v>
@@ -30422,10 +30422,10 @@
         <v>321</v>
       </c>
       <c r="X39" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="Y39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -30504,7 +30504,7 @@
         <v>321</v>
       </c>
       <c r="Y40" t="n">
-        <v>321</v>
+        <v>321.0000000000378</v>
       </c>
     </row>
     <row r="41">
@@ -30535,7 +30535,7 @@
         <v>321</v>
       </c>
       <c r="I41" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30602,16 +30602,16 @@
         <v>321</v>
       </c>
       <c r="E42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>147.4081841180268</v>
+        <v>321</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I42" t="n">
         <v>191.6509141932353</v>
@@ -30647,16 +30647,16 @@
         <v>321</v>
       </c>
       <c r="T42" t="n">
-        <v>321</v>
+        <v>147.4081841180267</v>
       </c>
       <c r="U42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X42" t="n">
         <v>321</v>
@@ -30696,7 +30696,7 @@
         <v>321</v>
       </c>
       <c r="J43" t="n">
-        <v>321</v>
+        <v>321.0000000000751</v>
       </c>
       <c r="K43" t="n">
         <v>321</v>
@@ -30802,7 +30802,7 @@
         <v>164.009091290606</v>
       </c>
       <c r="S44" t="n">
-        <v>320.539412634686</v>
+        <v>321</v>
       </c>
       <c r="T44" t="n">
         <v>321</v>
@@ -30833,16 +30833,16 @@
         <v>321</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>226.036732227374</v>
       </c>
       <c r="D45" t="n">
-        <v>147.4081841180269</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>321</v>
@@ -30875,7 +30875,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>321</v>
@@ -30890,7 +30890,7 @@
         <v>321</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W45" t="n">
         <v>321</v>
@@ -30972,7 +30972,7 @@
         <v>321</v>
       </c>
       <c r="W46" t="n">
-        <v>321</v>
+        <v>321.0000000000878</v>
       </c>
       <c r="X46" t="n">
         <v>321</v>
@@ -31091,49 +31091,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H2" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I2" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J2" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K2" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M2" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N2" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O2" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P2" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q2" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R2" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S2" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T2" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31170,49 +31170,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H3" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I3" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J3" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K3" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L3" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M3" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O3" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P3" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q3" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R3" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S3" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31249,49 +31249,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H4" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I4" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J4" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K4" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L4" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M4" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N4" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O4" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P4" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R4" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S4" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T4" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31328,49 +31328,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H5" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I5" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J5" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K5" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L5" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M5" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N5" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O5" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P5" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q5" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R5" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S5" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T5" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31407,49 +31407,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H6" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I6" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J6" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K6" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L6" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M6" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O6" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P6" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R6" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S6" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31486,49 +31486,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H7" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I7" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J7" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K7" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L7" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M7" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N7" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O7" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P7" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R7" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S7" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T7" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31565,49 +31565,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H8" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I8" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J8" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K8" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M8" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N8" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O8" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P8" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q8" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R8" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S8" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T8" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31644,49 +31644,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H9" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I9" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J9" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K9" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L9" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M9" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O9" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P9" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q9" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R9" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S9" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31723,49 +31723,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H10" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I10" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J10" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K10" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L10" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M10" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N10" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O10" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P10" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R10" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S10" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T10" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -34743,13 +34743,13 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K2" t="n">
-        <v>52.1599296482412</v>
+        <v>374</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512562</v>
+        <v>65.34340703517591</v>
       </c>
       <c r="M2" t="n">
         <v>374</v>
@@ -34761,10 +34761,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>374</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q2" t="n">
-        <v>242.0199542155222</v>
+        <v>234.1880104510424</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K3" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L3" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M3" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N3" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O3" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P3" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34886,28 +34886,28 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>68.83877143375551</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,25 +34928,25 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T4" t="n">
-        <v>190.7613351330866</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0516415124273</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>29.70262567257716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K5" t="n">
-        <v>374</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517591</v>
       </c>
       <c r="M5" t="n">
         <v>374</v>
       </c>
       <c r="N5" t="n">
-        <v>374</v>
+        <v>234.28870772354</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q5" t="n">
-        <v>235.5012052109774</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35059,25 +35059,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K6" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L6" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M6" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N6" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O6" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P6" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35132,19 +35132,19 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I7" t="n">
-        <v>228.8979542159473</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J7" t="n">
-        <v>153.6799680551111</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>132.8490622644307</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,19 +35165,19 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>40.83199570698065</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T7" t="n">
-        <v>190.7613351330866</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0516415124273</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V7" t="n">
         <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>148.7680905456179</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -35220,22 +35220,22 @@
         <v>374</v>
       </c>
       <c r="K8" t="n">
-        <v>373.9999999999999</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517586</v>
       </c>
       <c r="M8" t="n">
-        <v>235.5012052109774</v>
+        <v>374</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>181.6174062160025</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q8" t="n">
         <v>374</v>
@@ -35296,25 +35296,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K9" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L9" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M9" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N9" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O9" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P9" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35351,37 +35351,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>63.9528716742219</v>
       </c>
       <c r="C10" t="n">
-        <v>59.26268369607483</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,19 +35402,19 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T10" t="n">
-        <v>190.7613351330866</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0516415124273</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
@@ -35454,19 +35454,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K11" t="n">
-        <v>609.8778844919133</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M11" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>649</v>
+        <v>397.807439363043</v>
       </c>
       <c r="O11" t="n">
         <v>162.757678164601</v>
@@ -35606,7 +35606,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H13" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I13" t="n">
         <v>163.0214951995539</v>
@@ -35697,22 +35697,22 @@
         <v>175.9119195979899</v>
       </c>
       <c r="L14" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M14" t="n">
         <v>649</v>
       </c>
       <c r="N14" t="n">
+        <v>4.355038036034114</v>
+      </c>
+      <c r="O14" t="n">
         <v>649</v>
-      </c>
-      <c r="O14" t="n">
-        <v>162.757678164601</v>
       </c>
       <c r="P14" t="n">
         <v>198.5777841804241</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.200256351209361</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K17" t="n">
         <v>175.9119195979899</v>
       </c>
       <c r="L17" t="n">
-        <v>218.2342914572864</v>
+        <v>649.0000000000001</v>
       </c>
       <c r="M17" t="n">
+        <v>221.8955197650528</v>
+      </c>
+      <c r="N17" t="n">
         <v>649</v>
-      </c>
-      <c r="N17" t="n">
-        <v>490.5973598714331</v>
       </c>
       <c r="O17" t="n">
         <v>162.757678164601</v>
@@ -35949,7 +35949,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q17" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36168,13 +36168,13 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K20" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L20" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M20" t="n">
-        <v>649</v>
+        <v>17.50927946942293</v>
       </c>
       <c r="N20" t="n">
         <v>649</v>
@@ -36186,7 +36186,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.200256351209361</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36402,7 +36402,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K23" t="n">
         <v>175.9119195979899</v>
@@ -36414,16 +36414,16 @@
         <v>649</v>
       </c>
       <c r="N23" t="n">
-        <v>649</v>
+        <v>40.17514405185732</v>
       </c>
       <c r="O23" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P23" t="n">
-        <v>198.5777841804241</v>
+        <v>649</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.661228307766413</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36554,7 +36554,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H25" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I25" t="n">
         <v>163.0214951995539</v>
@@ -36642,16 +36642,16 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K26" t="n">
-        <v>609.8778844919133</v>
+        <v>175.91191959799</v>
       </c>
       <c r="L26" t="n">
-        <v>218.2342914572864</v>
+        <v>218.2342914572865</v>
       </c>
       <c r="M26" t="n">
-        <v>649</v>
+        <v>487.637763911837</v>
       </c>
       <c r="N26" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="O26" t="n">
         <v>162.757678164601</v>
@@ -36660,7 +36660,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36885,22 +36885,22 @@
         <v>218.2342914572864</v>
       </c>
       <c r="M29" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="N29" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P29" t="n">
-        <v>198.5777841804241</v>
+        <v>648</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.661228307766413</v>
+        <v>200.2794165285949</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.975165261426056e-10</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -37116,13 +37116,13 @@
         <v>512.6348760697097</v>
       </c>
       <c r="K32" t="n">
-        <v>648.9999999999999</v>
+        <v>648.0000000000634</v>
       </c>
       <c r="L32" t="n">
-        <v>649</v>
+        <v>648.0000000000634</v>
       </c>
       <c r="M32" t="n">
-        <v>397.807439363043</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -37134,7 +37134,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>395.8478434035713</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37350,19 +37350,19 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K35" t="n">
-        <v>648.9999999999999</v>
+        <v>607.9182885325076</v>
       </c>
       <c r="L35" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M35" t="n">
-        <v>649</v>
+        <v>648.0000000000953</v>
       </c>
       <c r="N35" t="n">
-        <v>179.5731479057565</v>
+        <v>648.0000000000953</v>
       </c>
       <c r="O35" t="n">
         <v>162.757678164601</v>
@@ -37499,10 +37499,10 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G37" t="n">
-        <v>76.57645502732242</v>
+        <v>76.57645502735295</v>
       </c>
       <c r="H37" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I37" t="n">
         <v>163.0214951995539</v>
@@ -37590,13 +37590,13 @@
         <v>512.6348760697097</v>
       </c>
       <c r="K38" t="n">
-        <v>648.9999999999999</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L38" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M38" t="n">
-        <v>397.807439363043</v>
+        <v>648.0000000001098</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -37605,10 +37605,10 @@
         <v>162.757678164601</v>
       </c>
       <c r="P38" t="n">
-        <v>198.5777841804241</v>
+        <v>255.9108115064331</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37739,7 +37739,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H40" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I40" t="n">
         <v>163.0214951995539</v>
@@ -37790,7 +37790,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y40" t="n">
-        <v>33.53464715053764</v>
+        <v>33.53464715057545</v>
       </c>
     </row>
     <row r="41">
@@ -37824,28 +37824,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K41" t="n">
         <v>175.9119195979899</v>
       </c>
       <c r="L41" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M41" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>649</v>
+        <v>220.0907054905955</v>
       </c>
       <c r="O41" t="n">
-        <v>162.757678164601</v>
+        <v>648.0000000001244</v>
       </c>
       <c r="P41" t="n">
         <v>198.5777841804241</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.200256351209361</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37976,13 +37976,13 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H43" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I43" t="n">
         <v>163.0214951995539</v>
       </c>
       <c r="J43" t="n">
-        <v>329.5882314919611</v>
+        <v>329.5882314920362</v>
       </c>
       <c r="K43" t="n">
         <v>104.5500458709881</v>
@@ -38061,28 +38061,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K44" t="n">
         <v>175.9119195979899</v>
       </c>
       <c r="L44" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M44" t="n">
-        <v>649</v>
+        <v>648.0000000001535</v>
       </c>
       <c r="N44" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P44" t="n">
-        <v>198.5777841804241</v>
+        <v>255.9108115063895</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.200256351209361</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38213,7 +38213,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H46" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I46" t="n">
         <v>163.0214951995539</v>
@@ -38258,7 +38258,7 @@
         <v>121.8296897837838</v>
       </c>
       <c r="W46" t="n">
-        <v>94.62719016129032</v>
+        <v>94.62719016137814</v>
       </c>
       <c r="X46" t="n">
         <v>73.55635456989245</v>
